--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11465,6 +11465,127 @@
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>118079875</v>
+      </c>
+      <c r="B96" t="n">
+        <v>56491</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Slättesmyran (Slättesmyran), Ång</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>580439</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7053295</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -11470,7 +11470,7 @@
         <v>118079875</v>
       </c>
       <c r="B96" t="n">
-        <v>56491</v>
+        <v>56492</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -11700,10 +11700,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118488192</v>
+        <v>118488516</v>
       </c>
       <c r="B98" t="n">
-        <v>57306</v>
+        <v>90504</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11716,39 +11716,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580609</v>
+        <v>580610</v>
       </c>
       <c r="R98" t="n">
-        <v>7053171</v>
+        <v>7053237</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11780,7 +11775,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11790,7 +11785,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11817,10 +11812,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118488126</v>
+        <v>118488192</v>
       </c>
       <c r="B99" t="n">
-        <v>79469</v>
+        <v>57306</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11829,38 +11824,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580607</v>
+        <v>580609</v>
       </c>
       <c r="R99" t="n">
-        <v>7053151</v>
+        <v>7053171</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11929,10 +11929,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118488516</v>
+        <v>118488126</v>
       </c>
       <c r="B100" t="n">
-        <v>90504</v>
+        <v>79469</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11941,25 +11941,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11969,10 +11969,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580610</v>
+        <v>580607</v>
       </c>
       <c r="R100" t="n">
-        <v>7053237</v>
+        <v>7053151</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD100" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -11588,10 +11588,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118489089</v>
+        <v>118488126</v>
       </c>
       <c r="B97" t="n">
-        <v>78484</v>
+        <v>79469</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11600,25 +11600,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11628,10 +11628,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580604</v>
+        <v>580607</v>
       </c>
       <c r="R97" t="n">
-        <v>7053205</v>
+        <v>7053151</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11700,10 +11700,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118488516</v>
+        <v>118489286</v>
       </c>
       <c r="B98" t="n">
-        <v>90504</v>
+        <v>90518</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11716,21 +11716,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11740,10 +11740,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580610</v>
+        <v>580600</v>
       </c>
       <c r="R98" t="n">
-        <v>7053237</v>
+        <v>7053230</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11812,10 +11812,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118488192</v>
+        <v>118488516</v>
       </c>
       <c r="B99" t="n">
-        <v>57306</v>
+        <v>90504</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11828,39 +11828,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580609</v>
+        <v>580610</v>
       </c>
       <c r="R99" t="n">
-        <v>7053171</v>
+        <v>7053237</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11892,7 +11887,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11902,7 +11897,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11929,10 +11924,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118488126</v>
+        <v>118488443</v>
       </c>
       <c r="B100" t="n">
-        <v>79469</v>
+        <v>90788</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11941,25 +11936,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11969,13 +11964,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580607</v>
+        <v>580608</v>
       </c>
       <c r="R100" t="n">
-        <v>7053151</v>
+        <v>7053200</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12002,19 +11997,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>20:27</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>20:27</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12029,22 +12014,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118488356</v>
+        <v>118488192</v>
       </c>
       <c r="B101" t="n">
-        <v>90788</v>
+        <v>57306</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12057,34 +12042,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580594</v>
+        <v>580609</v>
       </c>
       <c r="R101" t="n">
-        <v>7053187</v>
+        <v>7053171</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12116,7 +12106,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12126,7 +12116,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12153,10 +12143,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118488957</v>
+        <v>118488770</v>
       </c>
       <c r="B102" t="n">
-        <v>100080</v>
+        <v>97846</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12165,38 +12155,47 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1365</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580589</v>
+        <v>580601</v>
       </c>
       <c r="R102" t="n">
-        <v>7053237</v>
+        <v>7053271</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12228,7 +12227,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12238,7 +12237,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12265,10 +12264,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118488443</v>
+        <v>118489089</v>
       </c>
       <c r="B103" t="n">
-        <v>90788</v>
+        <v>78484</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12281,21 +12280,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12305,13 +12304,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580608</v>
+        <v>580604</v>
       </c>
       <c r="R103" t="n">
-        <v>7053200</v>
+        <v>7053205</v>
       </c>
       <c r="S103" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12338,9 +12337,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12355,22 +12364,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118488409</v>
+        <v>118489062</v>
       </c>
       <c r="B104" t="n">
-        <v>90504</v>
+        <v>90522</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12383,21 +12392,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12407,10 +12416,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580602</v>
+        <v>580605</v>
       </c>
       <c r="R104" t="n">
-        <v>7053185</v>
+        <v>7053216</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12442,7 +12451,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12452,7 +12461,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12479,10 +12488,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118488102</v>
+        <v>118488356</v>
       </c>
       <c r="B105" t="n">
-        <v>90947</v>
+        <v>90788</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12491,25 +12500,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12519,10 +12528,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580607</v>
+        <v>580594</v>
       </c>
       <c r="R105" t="n">
-        <v>7053151</v>
+        <v>7053187</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12554,7 +12563,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12564,7 +12573,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12591,10 +12600,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118489286</v>
+        <v>118488097</v>
       </c>
       <c r="B106" t="n">
-        <v>90518</v>
+        <v>90788</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12607,21 +12616,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12631,10 +12640,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580600</v>
+        <v>580612</v>
       </c>
       <c r="R106" t="n">
-        <v>7053230</v>
+        <v>7053150</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12666,7 +12675,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12676,7 +12685,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12703,10 +12712,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118488097</v>
+        <v>118488409</v>
       </c>
       <c r="B107" t="n">
-        <v>90788</v>
+        <v>90504</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12719,21 +12728,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12743,10 +12752,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580612</v>
+        <v>580602</v>
       </c>
       <c r="R107" t="n">
-        <v>7053150</v>
+        <v>7053185</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12778,7 +12787,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12788,7 +12797,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12815,10 +12824,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118488770</v>
+        <v>118489403</v>
       </c>
       <c r="B108" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12827,47 +12836,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580601</v>
+        <v>580611</v>
       </c>
       <c r="R108" t="n">
-        <v>7053271</v>
+        <v>7053232</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12936,10 +12936,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118489062</v>
+        <v>118488102</v>
       </c>
       <c r="B109" t="n">
-        <v>90522</v>
+        <v>90947</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12948,25 +12948,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>580605</v>
+        <v>580607</v>
       </c>
       <c r="R109" t="n">
-        <v>7053216</v>
+        <v>7053151</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13048,10 +13048,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118489403</v>
+        <v>118488957</v>
       </c>
       <c r="B110" t="n">
-        <v>90504</v>
+        <v>100080</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13060,25 +13060,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13088,10 +13088,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>580611</v>
+        <v>580589</v>
       </c>
       <c r="R110" t="n">
-        <v>7053232</v>
+        <v>7053237</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13123,7 +13123,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -11588,10 +11588,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118488126</v>
+        <v>118489286</v>
       </c>
       <c r="B97" t="n">
-        <v>79469</v>
+        <v>90518</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11600,25 +11600,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6456</v>
+        <v>1204</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11628,10 +11628,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580607</v>
+        <v>580600</v>
       </c>
       <c r="R97" t="n">
-        <v>7053151</v>
+        <v>7053230</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11700,10 +11700,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118489286</v>
+        <v>118489062</v>
       </c>
       <c r="B98" t="n">
-        <v>90518</v>
+        <v>90522</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11716,21 +11716,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11740,10 +11740,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580600</v>
+        <v>580605</v>
       </c>
       <c r="R98" t="n">
-        <v>7053230</v>
+        <v>7053216</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11812,10 +11812,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118488516</v>
+        <v>118489089</v>
       </c>
       <c r="B99" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11828,21 +11828,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580610</v>
+        <v>580604</v>
       </c>
       <c r="R99" t="n">
-        <v>7053237</v>
+        <v>7053205</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11924,10 +11924,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118488443</v>
+        <v>118488770</v>
       </c>
       <c r="B100" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11936,41 +11936,50 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580608</v>
+        <v>580601</v>
       </c>
       <c r="R100" t="n">
-        <v>7053200</v>
+        <v>7053271</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11997,9 +12006,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12014,22 +12033,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118488192</v>
+        <v>118488102</v>
       </c>
       <c r="B101" t="n">
-        <v>57306</v>
+        <v>90947</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12038,43 +12057,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580609</v>
+        <v>580607</v>
       </c>
       <c r="R101" t="n">
-        <v>7053171</v>
+        <v>7053151</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12106,7 +12120,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12116,7 +12130,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12143,10 +12157,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118488770</v>
+        <v>118488356</v>
       </c>
       <c r="B102" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12155,47 +12169,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580601</v>
+        <v>580594</v>
       </c>
       <c r="R102" t="n">
-        <v>7053271</v>
+        <v>7053187</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12227,7 +12232,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12237,7 +12242,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12264,10 +12269,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118489089</v>
+        <v>118488443</v>
       </c>
       <c r="B103" t="n">
-        <v>78484</v>
+        <v>90788</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12280,21 +12285,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12304,13 +12309,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580604</v>
+        <v>580608</v>
       </c>
       <c r="R103" t="n">
-        <v>7053205</v>
+        <v>7053200</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12337,19 +12342,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>21:08</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>21:08</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12364,22 +12359,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118489062</v>
+        <v>118488192</v>
       </c>
       <c r="B104" t="n">
-        <v>90522</v>
+        <v>57306</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12392,34 +12387,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580605</v>
+        <v>580609</v>
       </c>
       <c r="R104" t="n">
-        <v>7053216</v>
+        <v>7053171</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12488,10 +12488,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118488356</v>
+        <v>118488409</v>
       </c>
       <c r="B105" t="n">
-        <v>90788</v>
+        <v>90504</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12504,21 +12504,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12528,10 +12528,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580594</v>
+        <v>580602</v>
       </c>
       <c r="R105" t="n">
-        <v>7053187</v>
+        <v>7053185</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12600,10 +12600,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118488097</v>
+        <v>118488516</v>
       </c>
       <c r="B106" t="n">
-        <v>90788</v>
+        <v>90504</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12616,21 +12616,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12640,10 +12640,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580612</v>
+        <v>580610</v>
       </c>
       <c r="R106" t="n">
-        <v>7053150</v>
+        <v>7053237</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12712,10 +12712,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118488409</v>
+        <v>118488126</v>
       </c>
       <c r="B107" t="n">
-        <v>90504</v>
+        <v>79469</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12724,25 +12724,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12752,10 +12752,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580602</v>
+        <v>580607</v>
       </c>
       <c r="R107" t="n">
-        <v>7053185</v>
+        <v>7053151</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12824,10 +12824,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118489403</v>
+        <v>118488097</v>
       </c>
       <c r="B108" t="n">
-        <v>90504</v>
+        <v>90788</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12840,21 +12840,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12864,10 +12864,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580611</v>
+        <v>580612</v>
       </c>
       <c r="R108" t="n">
-        <v>7053232</v>
+        <v>7053150</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12936,10 +12936,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118488102</v>
+        <v>118488957</v>
       </c>
       <c r="B109" t="n">
-        <v>90947</v>
+        <v>100080</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12948,25 +12948,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1209</v>
+        <v>1365</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>580607</v>
+        <v>580589</v>
       </c>
       <c r="R109" t="n">
-        <v>7053151</v>
+        <v>7053237</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13048,10 +13048,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118488957</v>
+        <v>118489403</v>
       </c>
       <c r="B110" t="n">
-        <v>100080</v>
+        <v>90504</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13060,25 +13060,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13088,10 +13088,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>580589</v>
+        <v>580611</v>
       </c>
       <c r="R110" t="n">
-        <v>7053237</v>
+        <v>7053232</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13123,7 +13123,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -11588,10 +11588,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118489286</v>
+        <v>118488097</v>
       </c>
       <c r="B97" t="n">
-        <v>90518</v>
+        <v>90795</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11604,21 +11604,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11628,10 +11628,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580600</v>
+        <v>580612</v>
       </c>
       <c r="R97" t="n">
-        <v>7053230</v>
+        <v>7053150</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11700,10 +11700,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118489062</v>
+        <v>118488192</v>
       </c>
       <c r="B98" t="n">
-        <v>90522</v>
+        <v>57306</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11716,34 +11716,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580605</v>
+        <v>580609</v>
       </c>
       <c r="R98" t="n">
-        <v>7053216</v>
+        <v>7053171</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11775,7 +11780,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11785,7 +11790,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11812,10 +11817,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118489089</v>
+        <v>118488957</v>
       </c>
       <c r="B99" t="n">
-        <v>78484</v>
+        <v>100087</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11824,25 +11829,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11852,10 +11857,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580604</v>
+        <v>580589</v>
       </c>
       <c r="R99" t="n">
-        <v>7053205</v>
+        <v>7053237</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11887,7 +11892,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11897,7 +11902,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11924,10 +11929,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118488770</v>
+        <v>118488126</v>
       </c>
       <c r="B100" t="n">
-        <v>97846</v>
+        <v>79476</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11936,47 +11941,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580601</v>
+        <v>580607</v>
       </c>
       <c r="R100" t="n">
-        <v>7053271</v>
+        <v>7053151</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12008,7 +12004,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12018,7 +12014,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12045,10 +12041,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118488102</v>
+        <v>118489403</v>
       </c>
       <c r="B101" t="n">
-        <v>90947</v>
+        <v>90511</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12057,25 +12053,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12085,10 +12081,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580607</v>
+        <v>580611</v>
       </c>
       <c r="R101" t="n">
-        <v>7053151</v>
+        <v>7053232</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12120,7 +12116,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12130,7 +12126,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12160,7 +12156,7 @@
         <v>118488356</v>
       </c>
       <c r="B102" t="n">
-        <v>90788</v>
+        <v>90795</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12269,10 +12265,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118488443</v>
+        <v>118489286</v>
       </c>
       <c r="B103" t="n">
-        <v>90788</v>
+        <v>90525</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12285,21 +12281,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12309,13 +12305,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580608</v>
+        <v>580600</v>
       </c>
       <c r="R103" t="n">
-        <v>7053200</v>
+        <v>7053230</v>
       </c>
       <c r="S103" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12342,9 +12338,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12359,22 +12365,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118488192</v>
+        <v>118488516</v>
       </c>
       <c r="B104" t="n">
-        <v>57306</v>
+        <v>90511</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12387,39 +12393,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580609</v>
+        <v>580610</v>
       </c>
       <c r="R104" t="n">
-        <v>7053171</v>
+        <v>7053237</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12451,7 +12452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12461,7 +12462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12488,10 +12489,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118488409</v>
+        <v>118488102</v>
       </c>
       <c r="B105" t="n">
-        <v>90504</v>
+        <v>90954</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12500,25 +12501,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12528,10 +12529,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580602</v>
+        <v>580607</v>
       </c>
       <c r="R105" t="n">
-        <v>7053185</v>
+        <v>7053151</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12563,7 +12564,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12573,7 +12574,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12600,10 +12601,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118488516</v>
+        <v>118488443</v>
       </c>
       <c r="B106" t="n">
-        <v>90504</v>
+        <v>90795</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12616,21 +12617,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12640,13 +12641,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580610</v>
+        <v>580608</v>
       </c>
       <c r="R106" t="n">
-        <v>7053237</v>
+        <v>7053200</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12673,19 +12674,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>20:41</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>20:41</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12700,22 +12691,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118488126</v>
+        <v>118488770</v>
       </c>
       <c r="B107" t="n">
-        <v>79469</v>
+        <v>97853</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12724,38 +12715,47 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580607</v>
+        <v>580601</v>
       </c>
       <c r="R107" t="n">
-        <v>7053151</v>
+        <v>7053271</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12824,10 +12824,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118488097</v>
+        <v>118489089</v>
       </c>
       <c r="B108" t="n">
-        <v>90788</v>
+        <v>78491</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12840,21 +12840,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12864,10 +12864,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580612</v>
+        <v>580604</v>
       </c>
       <c r="R108" t="n">
-        <v>7053150</v>
+        <v>7053205</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12936,10 +12936,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118488957</v>
+        <v>118488409</v>
       </c>
       <c r="B109" t="n">
-        <v>100080</v>
+        <v>90511</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12948,25 +12948,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12976,10 +12976,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>580589</v>
+        <v>580602</v>
       </c>
       <c r="R109" t="n">
-        <v>7053237</v>
+        <v>7053185</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13048,10 +13048,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118489403</v>
+        <v>118489062</v>
       </c>
       <c r="B110" t="n">
-        <v>90504</v>
+        <v>90529</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13064,21 +13064,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13088,10 +13088,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>580611</v>
+        <v>580605</v>
       </c>
       <c r="R110" t="n">
-        <v>7053232</v>
+        <v>7053216</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13123,7 +13123,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13160,10 +13160,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118516029</v>
+        <v>118516030</v>
       </c>
       <c r="B111" t="n">
-        <v>90847</v>
+        <v>79476</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13172,25 +13172,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13200,10 +13200,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>580614</v>
+        <v>580609</v>
       </c>
       <c r="R111" t="n">
-        <v>7053227</v>
+        <v>7053150</v>
       </c>
       <c r="S111" t="n">
         <v>20</v>
@@ -13262,10 +13262,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118516030</v>
+        <v>118516029</v>
       </c>
       <c r="B112" t="n">
-        <v>79469</v>
+        <v>90854</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13274,25 +13274,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13302,10 +13302,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>580609</v>
+        <v>580614</v>
       </c>
       <c r="R112" t="n">
-        <v>7053150</v>
+        <v>7053227</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -11588,7 +11588,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118488097</v>
+        <v>118488356</v>
       </c>
       <c r="B97" t="n">
         <v>90795</v>
@@ -11628,10 +11628,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580612</v>
+        <v>580594</v>
       </c>
       <c r="R97" t="n">
-        <v>7053150</v>
+        <v>7053187</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11700,10 +11700,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118488192</v>
+        <v>118489062</v>
       </c>
       <c r="B98" t="n">
-        <v>57306</v>
+        <v>90529</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11716,39 +11716,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580609</v>
+        <v>580605</v>
       </c>
       <c r="R98" t="n">
-        <v>7053171</v>
+        <v>7053216</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11780,7 +11775,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11790,7 +11785,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11817,10 +11812,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118488957</v>
+        <v>118488126</v>
       </c>
       <c r="B99" t="n">
-        <v>100087</v>
+        <v>79476</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11833,21 +11828,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1365</v>
+        <v>6456</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11857,10 +11852,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580589</v>
+        <v>580607</v>
       </c>
       <c r="R99" t="n">
-        <v>7053237</v>
+        <v>7053151</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11892,7 +11887,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11902,7 +11897,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11929,10 +11924,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118488126</v>
+        <v>118488516</v>
       </c>
       <c r="B100" t="n">
-        <v>79476</v>
+        <v>90511</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11941,25 +11936,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11969,10 +11964,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580607</v>
+        <v>580610</v>
       </c>
       <c r="R100" t="n">
-        <v>7053151</v>
+        <v>7053237</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12004,7 +11999,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12014,7 +12009,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12041,7 +12036,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118489403</v>
+        <v>118488409</v>
       </c>
       <c r="B101" t="n">
         <v>90511</v>
@@ -12081,10 +12076,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580611</v>
+        <v>580602</v>
       </c>
       <c r="R101" t="n">
-        <v>7053232</v>
+        <v>7053185</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12116,7 +12111,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12126,7 +12121,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12153,7 +12148,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118488356</v>
+        <v>118488097</v>
       </c>
       <c r="B102" t="n">
         <v>90795</v>
@@ -12193,10 +12188,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580594</v>
+        <v>580612</v>
       </c>
       <c r="R102" t="n">
-        <v>7053187</v>
+        <v>7053150</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12228,7 +12223,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12238,7 +12233,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12265,10 +12260,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118489286</v>
+        <v>118488102</v>
       </c>
       <c r="B103" t="n">
-        <v>90525</v>
+        <v>90954</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12277,25 +12272,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12305,10 +12300,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580600</v>
+        <v>580607</v>
       </c>
       <c r="R103" t="n">
-        <v>7053230</v>
+        <v>7053151</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12340,7 +12335,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12350,7 +12345,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12377,10 +12372,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118488516</v>
+        <v>118488192</v>
       </c>
       <c r="B104" t="n">
-        <v>90511</v>
+        <v>57306</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12393,34 +12388,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580610</v>
+        <v>580609</v>
       </c>
       <c r="R104" t="n">
-        <v>7053237</v>
+        <v>7053171</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12489,10 +12489,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118488102</v>
+        <v>118489403</v>
       </c>
       <c r="B105" t="n">
-        <v>90954</v>
+        <v>90511</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12501,25 +12501,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580607</v>
+        <v>580611</v>
       </c>
       <c r="R105" t="n">
-        <v>7053151</v>
+        <v>7053232</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12601,10 +12601,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118488443</v>
+        <v>118488957</v>
       </c>
       <c r="B106" t="n">
-        <v>90795</v>
+        <v>100087</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12613,25 +12613,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>1365</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12641,13 +12641,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580608</v>
+        <v>580589</v>
       </c>
       <c r="R106" t="n">
-        <v>7053200</v>
+        <v>7053237</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12674,9 +12674,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12691,22 +12701,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118488770</v>
+        <v>118489089</v>
       </c>
       <c r="B107" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12715,47 +12725,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580601</v>
+        <v>580604</v>
       </c>
       <c r="R107" t="n">
-        <v>7053271</v>
+        <v>7053205</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12787,7 +12788,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12797,7 +12798,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12824,10 +12825,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118489089</v>
+        <v>118488770</v>
       </c>
       <c r="B108" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12836,38 +12837,47 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580604</v>
+        <v>580601</v>
       </c>
       <c r="R108" t="n">
-        <v>7053205</v>
+        <v>7053271</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12899,7 +12909,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12909,7 +12919,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12936,10 +12946,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118488409</v>
+        <v>118488443</v>
       </c>
       <c r="B109" t="n">
-        <v>90511</v>
+        <v>90795</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12952,21 +12962,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12976,13 +12986,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>580602</v>
+        <v>580608</v>
       </c>
       <c r="R109" t="n">
-        <v>7053185</v>
+        <v>7053200</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13009,19 +13019,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>20:36</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>20:36</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13036,22 +13036,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118489062</v>
+        <v>118489286</v>
       </c>
       <c r="B110" t="n">
-        <v>90529</v>
+        <v>90525</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13064,21 +13064,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13088,10 +13088,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>580605</v>
+        <v>580600</v>
       </c>
       <c r="R110" t="n">
-        <v>7053216</v>
+        <v>7053230</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13123,7 +13123,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -14800,10 +14800,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120896112</v>
+        <v>120897551</v>
       </c>
       <c r="B126" t="n">
-        <v>95365</v>
+        <v>95375</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14836,17 +14836,17 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Slättesmyran, Ång</t>
+          <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>580482</v>
+        <v>580492</v>
       </c>
       <c r="R126" t="n">
-        <v>7053297</v>
+        <v>7053272</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14873,19 +14873,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14900,22 +14890,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120897551</v>
+        <v>120897746</v>
       </c>
       <c r="B127" t="n">
-        <v>95365</v>
+        <v>90644</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14924,25 +14914,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2869</v>
+        <v>112</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14952,13 +14942,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>580492</v>
+        <v>580486</v>
       </c>
       <c r="R127" t="n">
-        <v>7053272</v>
+        <v>7053291</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15014,10 +15004,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120896442</v>
+        <v>120897756</v>
       </c>
       <c r="B128" t="n">
-        <v>90652</v>
+        <v>90644</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15026,25 +15016,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15054,10 +15044,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>580500</v>
+        <v>580487</v>
       </c>
       <c r="R128" t="n">
-        <v>7053305</v>
+        <v>7053274</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15089,7 +15079,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15099,7 +15089,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15126,10 +15116,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120895561</v>
+        <v>120897610</v>
       </c>
       <c r="B129" t="n">
-        <v>95365</v>
+        <v>98081</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15138,25 +15128,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15166,13 +15156,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>580472</v>
+        <v>580489</v>
       </c>
       <c r="R129" t="n">
-        <v>7053314</v>
+        <v>7053263</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15199,19 +15189,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15226,22 +15206,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120895782</v>
+        <v>120896380</v>
       </c>
       <c r="B130" t="n">
-        <v>95365</v>
+        <v>91137</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15250,25 +15230,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2869</v>
+        <v>1209</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15278,13 +15258,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>580458</v>
+        <v>580477</v>
       </c>
       <c r="R130" t="n">
-        <v>7053304</v>
+        <v>7053274</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15340,10 +15320,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120896287</v>
+        <v>120895561</v>
       </c>
       <c r="B131" t="n">
-        <v>91127</v>
+        <v>95375</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15352,25 +15332,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1209</v>
+        <v>2869</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15380,10 +15360,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>580488</v>
+        <v>580472</v>
       </c>
       <c r="R131" t="n">
-        <v>7053300</v>
+        <v>7053314</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15415,7 +15395,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15425,7 +15405,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15452,10 +15432,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120897183</v>
+        <v>120896940</v>
       </c>
       <c r="B132" t="n">
-        <v>91963</v>
+        <v>91089</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15464,25 +15444,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15492,10 +15467,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>580490</v>
+        <v>580477</v>
       </c>
       <c r="R132" t="n">
-        <v>7053233</v>
+        <v>7053259</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15525,9 +15500,24 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15542,22 +15532,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120896185</v>
+        <v>120896228</v>
       </c>
       <c r="B133" t="n">
-        <v>90687</v>
+        <v>90711</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15570,21 +15560,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15594,10 +15584,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>580483</v>
+        <v>580486</v>
       </c>
       <c r="R133" t="n">
-        <v>7053297</v>
+        <v>7053298</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15629,7 +15619,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15639,7 +15629,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15666,10 +15656,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120896940</v>
+        <v>120897183</v>
       </c>
       <c r="B134" t="n">
-        <v>91079</v>
+        <v>91973</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15678,20 +15668,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6040162</v>
+        <v>4364</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15701,10 +15696,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>580477</v>
+        <v>580490</v>
       </c>
       <c r="R134" t="n">
-        <v>7053259</v>
+        <v>7053233</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15734,24 +15729,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15766,22 +15746,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120896391</v>
+        <v>120895782</v>
       </c>
       <c r="B135" t="n">
-        <v>82382</v>
+        <v>95375</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15790,25 +15770,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15818,13 +15798,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>580499</v>
+        <v>580458</v>
       </c>
       <c r="R135" t="n">
-        <v>7053308</v>
+        <v>7053304</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15851,19 +15831,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15878,22 +15848,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120896380</v>
+        <v>120895896</v>
       </c>
       <c r="B136" t="n">
-        <v>91127</v>
+        <v>90662</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15902,25 +15872,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15930,13 +15900,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>580477</v>
+        <v>580458</v>
       </c>
       <c r="R136" t="n">
-        <v>7053274</v>
+        <v>7053304</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15992,10 +15962,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120897756</v>
+        <v>120896287</v>
       </c>
       <c r="B137" t="n">
-        <v>90634</v>
+        <v>91137</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16004,25 +15974,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16032,10 +16002,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>580487</v>
+        <v>580488</v>
       </c>
       <c r="R137" t="n">
-        <v>7053274</v>
+        <v>7053300</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16067,7 +16037,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16077,7 +16047,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16104,10 +16074,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120895896</v>
+        <v>120896442</v>
       </c>
       <c r="B138" t="n">
-        <v>90652</v>
+        <v>90662</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16144,13 +16114,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>580458</v>
+        <v>580500</v>
       </c>
       <c r="R138" t="n">
-        <v>7053304</v>
+        <v>7053305</v>
       </c>
       <c r="S138" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16177,9 +16147,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16194,22 +16174,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120897610</v>
+        <v>120896185</v>
       </c>
       <c r="B139" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16218,25 +16198,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16246,13 +16226,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>580489</v>
+        <v>580483</v>
       </c>
       <c r="R139" t="n">
-        <v>7053263</v>
+        <v>7053297</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16279,9 +16259,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16296,22 +16286,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120897746</v>
+        <v>120895507</v>
       </c>
       <c r="B140" t="n">
-        <v>90634</v>
+        <v>78601</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16324,21 +16314,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16348,13 +16338,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>580486</v>
+        <v>580500</v>
       </c>
       <c r="R140" t="n">
-        <v>7053291</v>
+        <v>7053335</v>
       </c>
       <c r="S140" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16410,10 +16400,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120896228</v>
+        <v>120895803</v>
       </c>
       <c r="B141" t="n">
-        <v>90701</v>
+        <v>100320</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16422,25 +16412,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1204</v>
+        <v>1365</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16450,10 +16440,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>580486</v>
+        <v>580463</v>
       </c>
       <c r="R141" t="n">
-        <v>7053298</v>
+        <v>7053312</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16485,7 +16475,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16495,7 +16485,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16522,10 +16512,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120895803</v>
+        <v>120896112</v>
       </c>
       <c r="B142" t="n">
-        <v>100310</v>
+        <v>95375</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16538,37 +16528,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Slättesmyran, Slättesmyran, Ång</t>
+          <t>Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>580463</v>
+        <v>580482</v>
       </c>
       <c r="R142" t="n">
-        <v>7053312</v>
+        <v>7053297</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16597,7 +16587,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16607,7 +16597,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16634,10 +16624,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120895507</v>
+        <v>120896391</v>
       </c>
       <c r="B143" t="n">
-        <v>78598</v>
+        <v>82385</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16650,21 +16640,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16674,13 +16664,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>580500</v>
+        <v>580499</v>
       </c>
       <c r="R143" t="n">
-        <v>7053335</v>
+        <v>7053308</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16707,9 +16697,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16724,22 +16724,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121125943</v>
+        <v>121129042</v>
       </c>
       <c r="B144" t="n">
-        <v>98071</v>
+        <v>91965</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16748,25 +16748,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16776,10 +16776,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>580603</v>
+        <v>580421</v>
       </c>
       <c r="R144" t="n">
-        <v>7053117</v>
+        <v>7053299</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16848,10 +16848,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121127030</v>
+        <v>121128867</v>
       </c>
       <c r="B145" t="n">
-        <v>78598</v>
+        <v>95375</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16860,25 +16860,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16888,10 +16888,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>580528</v>
+        <v>580445</v>
       </c>
       <c r="R145" t="n">
-        <v>7053255</v>
+        <v>7053311</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16960,10 +16960,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121128867</v>
+        <v>121129017</v>
       </c>
       <c r="B146" t="n">
-        <v>95365</v>
+        <v>91973</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16976,21 +16976,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17000,10 +17000,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>580445</v>
+        <v>580426</v>
       </c>
       <c r="R146" t="n">
-        <v>7053311</v>
+        <v>7053283</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17072,10 +17072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121126027</v>
+        <v>121127030</v>
       </c>
       <c r="B147" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17088,44 +17088,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>580590</v>
+        <v>580528</v>
       </c>
       <c r="R147" t="n">
-        <v>7053152</v>
+        <v>7053255</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17157,7 +17147,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17167,7 +17157,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17194,10 +17184,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121125921</v>
+        <v>121127278</v>
       </c>
       <c r="B148" t="n">
-        <v>57348</v>
+        <v>90662</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17206,48 +17196,38 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>580600</v>
+        <v>580510</v>
       </c>
       <c r="R148" t="n">
-        <v>7053106</v>
+        <v>7053247</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17279,7 +17259,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17289,7 +17269,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17316,10 +17296,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121129042</v>
+        <v>121126181</v>
       </c>
       <c r="B149" t="n">
-        <v>91955</v>
+        <v>95375</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17328,25 +17308,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4361</v>
+        <v>2869</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17356,10 +17336,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>580421</v>
+        <v>580568</v>
       </c>
       <c r="R149" t="n">
-        <v>7053299</v>
+        <v>7053195</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17391,7 +17371,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17401,7 +17381,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17428,10 +17408,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121126214</v>
+        <v>121127564</v>
       </c>
       <c r="B150" t="n">
-        <v>78598</v>
+        <v>91973</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17440,25 +17420,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17468,10 +17448,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>580564</v>
+        <v>580441</v>
       </c>
       <c r="R150" t="n">
-        <v>7053209</v>
+        <v>7053267</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17503,7 +17483,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17513,7 +17493,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17540,10 +17520,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121126868</v>
+        <v>121126214</v>
       </c>
       <c r="B151" t="n">
-        <v>91079</v>
+        <v>78601</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17556,16 +17536,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6040162</v>
+        <v>6425</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17575,10 +17560,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>580542</v>
+        <v>580564</v>
       </c>
       <c r="R151" t="n">
-        <v>7053234</v>
+        <v>7053209</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17610,7 +17595,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17620,7 +17605,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17635,22 +17620,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121128951</v>
+        <v>121126027</v>
       </c>
       <c r="B152" t="n">
-        <v>79679</v>
+        <v>57351</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17663,34 +17648,44 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>580424</v>
+        <v>580590</v>
       </c>
       <c r="R152" t="n">
-        <v>7053312</v>
+        <v>7053152</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17722,7 +17717,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17732,7 +17727,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17759,10 +17754,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121127710</v>
+        <v>121125921</v>
       </c>
       <c r="B153" t="n">
-        <v>91955</v>
+        <v>57351</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17775,34 +17770,44 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>580426</v>
+        <v>580600</v>
       </c>
       <c r="R153" t="n">
-        <v>7053263</v>
+        <v>7053106</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17834,7 +17839,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17844,7 +17849,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17871,10 +17876,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121126694</v>
+        <v>121127289</v>
       </c>
       <c r="B154" t="n">
-        <v>98071</v>
+        <v>95375</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17883,42 +17888,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>580565</v>
+        <v>580508</v>
       </c>
       <c r="R154" t="n">
-        <v>7053263</v>
+        <v>7053256</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17950,7 +17951,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17960,7 +17961,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17987,10 +17988,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121126610</v>
+        <v>121128951</v>
       </c>
       <c r="B155" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17999,42 +18000,38 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>580564</v>
+        <v>580424</v>
       </c>
       <c r="R155" t="n">
-        <v>7053248</v>
+        <v>7053312</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18066,7 +18063,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18076,7 +18073,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18091,22 +18088,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121127803</v>
+        <v>121126530</v>
       </c>
       <c r="B156" t="n">
-        <v>56560</v>
+        <v>78601</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18115,43 +18112,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>580418</v>
+        <v>580571</v>
       </c>
       <c r="R156" t="n">
-        <v>7053258</v>
+        <v>7053237</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18183,7 +18175,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18193,7 +18185,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18220,10 +18212,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121126972</v>
+        <v>121126868</v>
       </c>
       <c r="B157" t="n">
-        <v>82382</v>
+        <v>91089</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18236,21 +18228,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18260,7 +18247,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>580535</v>
+        <v>580542</v>
       </c>
       <c r="R157" t="n">
         <v>7053234</v>
@@ -18295,7 +18282,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18305,7 +18292,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18320,22 +18307,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121127610</v>
+        <v>121126972</v>
       </c>
       <c r="B158" t="n">
-        <v>91963</v>
+        <v>82385</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18344,25 +18331,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18372,10 +18359,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>580433</v>
+        <v>580535</v>
       </c>
       <c r="R158" t="n">
-        <v>7053267</v>
+        <v>7053234</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18407,7 +18394,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18417,7 +18404,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18444,10 +18431,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121127564</v>
+        <v>121127803</v>
       </c>
       <c r="B159" t="n">
-        <v>91963</v>
+        <v>56563</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18460,34 +18447,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>580441</v>
+        <v>580418</v>
       </c>
       <c r="R159" t="n">
-        <v>7053267</v>
+        <v>7053258</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18519,7 +18511,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18529,7 +18521,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18556,10 +18548,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121129017</v>
+        <v>121126610</v>
       </c>
       <c r="B160" t="n">
-        <v>91963</v>
+        <v>98081</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18568,38 +18560,42 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>580426</v>
+        <v>580564</v>
       </c>
       <c r="R160" t="n">
-        <v>7053283</v>
+        <v>7053248</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18631,7 +18627,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18641,7 +18637,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18656,22 +18652,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121127289</v>
+        <v>121126643</v>
       </c>
       <c r="B161" t="n">
-        <v>95365</v>
+        <v>78601</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18680,25 +18676,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18708,10 +18704,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>580508</v>
+        <v>580565</v>
       </c>
       <c r="R161" t="n">
-        <v>7053256</v>
+        <v>7053263</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18743,7 +18739,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18753,7 +18749,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18780,10 +18776,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121126530</v>
+        <v>121126694</v>
       </c>
       <c r="B162" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18792,38 +18788,42 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>580571</v>
+        <v>580565</v>
       </c>
       <c r="R162" t="n">
-        <v>7053237</v>
+        <v>7053263</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18892,10 +18892,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121126181</v>
+        <v>121126779</v>
       </c>
       <c r="B163" t="n">
-        <v>95365</v>
+        <v>78601</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18904,25 +18904,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18932,10 +18932,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>580568</v>
+        <v>580548</v>
       </c>
       <c r="R163" t="n">
-        <v>7053195</v>
+        <v>7053237</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18977,7 +18977,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19004,10 +19004,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121126876</v>
+        <v>121127610</v>
       </c>
       <c r="B164" t="n">
-        <v>78598</v>
+        <v>91973</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19016,25 +19016,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19044,10 +19044,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>580540</v>
+        <v>580433</v>
       </c>
       <c r="R164" t="n">
-        <v>7053257</v>
+        <v>7053267</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19116,10 +19116,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121127278</v>
+        <v>121126876</v>
       </c>
       <c r="B165" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19128,25 +19128,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19156,10 +19156,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>580510</v>
+        <v>580540</v>
       </c>
       <c r="R165" t="n">
-        <v>7053247</v>
+        <v>7053257</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19228,10 +19228,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121126779</v>
+        <v>121125943</v>
       </c>
       <c r="B166" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19240,25 +19240,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>580548</v>
+        <v>580603</v>
       </c>
       <c r="R166" t="n">
-        <v>7053237</v>
+        <v>7053117</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19303,7 +19303,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19340,10 +19340,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121126643</v>
+        <v>121127710</v>
       </c>
       <c r="B167" t="n">
-        <v>78598</v>
+        <v>91965</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19356,21 +19356,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>580565</v>
+        <v>580426</v>
       </c>
       <c r="R167" t="n">
         <v>7053263</v>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -16400,10 +16400,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120895803</v>
+        <v>120896112</v>
       </c>
       <c r="B141" t="n">
-        <v>100320</v>
+        <v>95375</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16416,37 +16416,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Slättesmyran, Slättesmyran, Ång</t>
+          <t>Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>580463</v>
+        <v>580482</v>
       </c>
       <c r="R141" t="n">
-        <v>7053312</v>
+        <v>7053297</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16485,7 +16485,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16512,10 +16512,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120896112</v>
+        <v>120895803</v>
       </c>
       <c r="B142" t="n">
-        <v>95375</v>
+        <v>100320</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16528,37 +16528,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Slättesmyran, Ång</t>
+          <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>580482</v>
+        <v>580463</v>
       </c>
       <c r="R142" t="n">
-        <v>7053297</v>
+        <v>7053312</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17876,10 +17876,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121127289</v>
+        <v>121128951</v>
       </c>
       <c r="B154" t="n">
-        <v>95375</v>
+        <v>79682</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17888,25 +17888,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17916,10 +17916,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>580508</v>
+        <v>580424</v>
       </c>
       <c r="R154" t="n">
-        <v>7053256</v>
+        <v>7053312</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17988,10 +17988,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121128951</v>
+        <v>121127289</v>
       </c>
       <c r="B155" t="n">
-        <v>79682</v>
+        <v>95375</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18000,25 +18000,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18028,10 +18028,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>580424</v>
+        <v>580508</v>
       </c>
       <c r="R155" t="n">
-        <v>7053312</v>
+        <v>7053256</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -19004,10 +19004,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121127610</v>
+        <v>121126876</v>
       </c>
       <c r="B164" t="n">
-        <v>91973</v>
+        <v>78601</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19016,25 +19016,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19044,10 +19044,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>580433</v>
+        <v>580540</v>
       </c>
       <c r="R164" t="n">
-        <v>7053267</v>
+        <v>7053257</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19116,10 +19116,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121126876</v>
+        <v>121125943</v>
       </c>
       <c r="B165" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19128,25 +19128,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19156,10 +19156,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>580540</v>
+        <v>580603</v>
       </c>
       <c r="R165" t="n">
-        <v>7053257</v>
+        <v>7053117</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19228,10 +19228,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121125943</v>
+        <v>121127610</v>
       </c>
       <c r="B166" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19240,25 +19240,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>580603</v>
+        <v>580433</v>
       </c>
       <c r="R166" t="n">
-        <v>7053117</v>
+        <v>7053267</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19303,7 +19303,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD166" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -16400,10 +16400,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120896112</v>
+        <v>120895803</v>
       </c>
       <c r="B141" t="n">
-        <v>95375</v>
+        <v>100320</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16416,37 +16416,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Slättesmyran, Ång</t>
+          <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>580482</v>
+        <v>580463</v>
       </c>
       <c r="R141" t="n">
-        <v>7053297</v>
+        <v>7053312</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16485,7 +16485,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16512,10 +16512,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120895803</v>
+        <v>120896112</v>
       </c>
       <c r="B142" t="n">
-        <v>100320</v>
+        <v>95375</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16528,37 +16528,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1365</v>
+        <v>2869</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Slättesmyran, Slättesmyran, Ång</t>
+          <t>Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>580463</v>
+        <v>580482</v>
       </c>
       <c r="R142" t="n">
-        <v>7053312</v>
+        <v>7053297</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -19004,10 +19004,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121126876</v>
+        <v>121127610</v>
       </c>
       <c r="B164" t="n">
-        <v>78601</v>
+        <v>91973</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19016,25 +19016,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19044,10 +19044,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>580540</v>
+        <v>580433</v>
       </c>
       <c r="R164" t="n">
-        <v>7053257</v>
+        <v>7053267</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19116,10 +19116,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121125943</v>
+        <v>121126876</v>
       </c>
       <c r="B165" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19128,25 +19128,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19156,10 +19156,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>580603</v>
+        <v>580540</v>
       </c>
       <c r="R165" t="n">
-        <v>7053117</v>
+        <v>7053257</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19228,10 +19228,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121127610</v>
+        <v>121125943</v>
       </c>
       <c r="B166" t="n">
-        <v>91973</v>
+        <v>98081</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19240,25 +19240,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>580433</v>
+        <v>580603</v>
       </c>
       <c r="R166" t="n">
-        <v>7053267</v>
+        <v>7053117</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19303,7 +19303,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD166" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -14800,10 +14800,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120897551</v>
+        <v>120896228</v>
       </c>
       <c r="B126" t="n">
-        <v>95375</v>
+        <v>90711</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14812,25 +14812,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2869</v>
+        <v>1204</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14840,13 +14840,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>580492</v>
+        <v>580486</v>
       </c>
       <c r="R126" t="n">
-        <v>7053272</v>
+        <v>7053298</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14873,9 +14873,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14890,22 +14900,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120897746</v>
+        <v>120896380</v>
       </c>
       <c r="B127" t="n">
-        <v>90644</v>
+        <v>91137</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14914,25 +14924,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14942,13 +14952,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>580486</v>
+        <v>580477</v>
       </c>
       <c r="R127" t="n">
-        <v>7053291</v>
+        <v>7053274</v>
       </c>
       <c r="S127" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15004,10 +15014,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120897756</v>
+        <v>120896391</v>
       </c>
       <c r="B128" t="n">
-        <v>90644</v>
+        <v>82385</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15020,21 +15030,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15044,10 +15054,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>580487</v>
+        <v>580499</v>
       </c>
       <c r="R128" t="n">
-        <v>7053274</v>
+        <v>7053308</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15079,7 +15089,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15089,7 +15099,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15116,10 +15126,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120897610</v>
+        <v>120895803</v>
       </c>
       <c r="B129" t="n">
-        <v>98081</v>
+        <v>100320</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15128,25 +15138,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15156,13 +15166,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>580489</v>
+        <v>580463</v>
       </c>
       <c r="R129" t="n">
-        <v>7053263</v>
+        <v>7053312</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15189,9 +15199,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15206,22 +15226,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120896380</v>
+        <v>120896442</v>
       </c>
       <c r="B130" t="n">
-        <v>91137</v>
+        <v>90662</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15230,25 +15250,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15258,10 +15278,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>580477</v>
+        <v>580500</v>
       </c>
       <c r="R130" t="n">
-        <v>7053274</v>
+        <v>7053305</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15291,9 +15311,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15308,22 +15338,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120895561</v>
+        <v>120895507</v>
       </c>
       <c r="B131" t="n">
-        <v>95375</v>
+        <v>78601</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15332,25 +15362,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15360,13 +15390,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>580472</v>
+        <v>580500</v>
       </c>
       <c r="R131" t="n">
-        <v>7053314</v>
+        <v>7053335</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15393,19 +15423,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15420,22 +15440,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120896940</v>
+        <v>120895561</v>
       </c>
       <c r="B132" t="n">
-        <v>91089</v>
+        <v>95375</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15444,20 +15464,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6040162</v>
+        <v>2869</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15467,10 +15492,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>580477</v>
+        <v>580472</v>
       </c>
       <c r="R132" t="n">
-        <v>7053259</v>
+        <v>7053314</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15502,7 +15527,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15512,12 +15537,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15544,10 +15564,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120896228</v>
+        <v>120896185</v>
       </c>
       <c r="B133" t="n">
-        <v>90711</v>
+        <v>90697</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15560,21 +15580,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15584,10 +15604,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>580486</v>
+        <v>580483</v>
       </c>
       <c r="R133" t="n">
-        <v>7053298</v>
+        <v>7053297</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15619,7 +15639,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15629,7 +15649,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15656,10 +15676,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120897183</v>
+        <v>120896112</v>
       </c>
       <c r="B134" t="n">
-        <v>91973</v>
+        <v>95375</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15672,37 +15692,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Slättesmyran, Slättesmyran, Ång</t>
+          <t>Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>580490</v>
+        <v>580482</v>
       </c>
       <c r="R134" t="n">
-        <v>7053233</v>
+        <v>7053297</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15729,9 +15749,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15746,22 +15776,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120895782</v>
+        <v>120897756</v>
       </c>
       <c r="B135" t="n">
-        <v>95375</v>
+        <v>90644</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15770,25 +15800,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2869</v>
+        <v>112</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15798,13 +15828,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>580458</v>
+        <v>580487</v>
       </c>
       <c r="R135" t="n">
-        <v>7053304</v>
+        <v>7053274</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15831,9 +15861,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15848,22 +15888,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120895896</v>
+        <v>120896287</v>
       </c>
       <c r="B136" t="n">
-        <v>90662</v>
+        <v>91137</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15872,25 +15912,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15900,13 +15940,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>580458</v>
+        <v>580488</v>
       </c>
       <c r="R136" t="n">
-        <v>7053304</v>
+        <v>7053300</v>
       </c>
       <c r="S136" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15933,9 +15973,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15950,22 +16000,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120896287</v>
+        <v>120897746</v>
       </c>
       <c r="B137" t="n">
-        <v>91137</v>
+        <v>90644</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15974,25 +16024,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16002,13 +16052,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>580488</v>
+        <v>580486</v>
       </c>
       <c r="R137" t="n">
-        <v>7053300</v>
+        <v>7053291</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16035,19 +16085,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>12:11</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16062,22 +16102,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120896442</v>
+        <v>120896940</v>
       </c>
       <c r="B138" t="n">
-        <v>90662</v>
+        <v>91089</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16086,25 +16126,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16114,10 +16149,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>580500</v>
+        <v>580477</v>
       </c>
       <c r="R138" t="n">
-        <v>7053305</v>
+        <v>7053259</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16149,7 +16184,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16159,7 +16194,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16186,10 +16226,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120896185</v>
+        <v>120895782</v>
       </c>
       <c r="B139" t="n">
-        <v>90697</v>
+        <v>95375</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16198,25 +16238,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16226,13 +16266,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>580483</v>
+        <v>580458</v>
       </c>
       <c r="R139" t="n">
-        <v>7053297</v>
+        <v>7053304</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16259,19 +16299,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16286,22 +16316,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120895507</v>
+        <v>120897610</v>
       </c>
       <c r="B140" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16310,25 +16340,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16338,10 +16368,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>580500</v>
+        <v>580489</v>
       </c>
       <c r="R140" t="n">
-        <v>7053335</v>
+        <v>7053263</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16400,10 +16430,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120895803</v>
+        <v>120895896</v>
       </c>
       <c r="B141" t="n">
-        <v>100320</v>
+        <v>90662</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16416,21 +16446,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1365</v>
+        <v>5447</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16440,13 +16470,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>580463</v>
+        <v>580458</v>
       </c>
       <c r="R141" t="n">
-        <v>7053312</v>
+        <v>7053304</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16473,19 +16503,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16500,19 +16520,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120896112</v>
+        <v>120897551</v>
       </c>
       <c r="B142" t="n">
         <v>95375</v>
@@ -16548,17 +16568,17 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Slättesmyran, Ång</t>
+          <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>580482</v>
+        <v>580492</v>
       </c>
       <c r="R142" t="n">
-        <v>7053297</v>
+        <v>7053272</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16585,19 +16605,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16612,22 +16622,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120896391</v>
+        <v>120897183</v>
       </c>
       <c r="B143" t="n">
-        <v>82385</v>
+        <v>91973</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16636,25 +16646,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16664,10 +16674,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>580499</v>
+        <v>580490</v>
       </c>
       <c r="R143" t="n">
-        <v>7053308</v>
+        <v>7053233</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16697,19 +16707,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16724,19 +16724,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121129042</v>
+        <v>121127710</v>
       </c>
       <c r="B144" t="n">
         <v>91965</v>
@@ -16776,10 +16776,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>580421</v>
+        <v>580426</v>
       </c>
       <c r="R144" t="n">
-        <v>7053299</v>
+        <v>7053263</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16848,10 +16848,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121128867</v>
+        <v>121129017</v>
       </c>
       <c r="B145" t="n">
-        <v>95375</v>
+        <v>91973</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16864,21 +16864,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16888,10 +16888,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>580445</v>
+        <v>580426</v>
       </c>
       <c r="R145" t="n">
-        <v>7053311</v>
+        <v>7053283</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16960,10 +16960,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121129017</v>
+        <v>121128867</v>
       </c>
       <c r="B146" t="n">
-        <v>91973</v>
+        <v>95375</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16976,21 +16976,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17000,10 +17000,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>580426</v>
+        <v>580445</v>
       </c>
       <c r="R146" t="n">
-        <v>7053283</v>
+        <v>7053311</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17072,7 +17072,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121127030</v>
+        <v>121126214</v>
       </c>
       <c r="B147" t="n">
         <v>78601</v>
@@ -17112,10 +17112,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>580528</v>
+        <v>580564</v>
       </c>
       <c r="R147" t="n">
-        <v>7053255</v>
+        <v>7053209</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17184,10 +17184,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121127278</v>
+        <v>121125943</v>
       </c>
       <c r="B148" t="n">
-        <v>90662</v>
+        <v>98081</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17196,25 +17196,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17224,10 +17224,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>580510</v>
+        <v>580603</v>
       </c>
       <c r="R148" t="n">
-        <v>7053247</v>
+        <v>7053117</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17296,10 +17296,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121126181</v>
+        <v>121126779</v>
       </c>
       <c r="B149" t="n">
-        <v>95375</v>
+        <v>78601</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17308,25 +17308,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>580568</v>
+        <v>580548</v>
       </c>
       <c r="R149" t="n">
-        <v>7053195</v>
+        <v>7053237</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17408,10 +17408,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121127564</v>
+        <v>121129042</v>
       </c>
       <c r="B150" t="n">
-        <v>91973</v>
+        <v>91965</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17420,25 +17420,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17448,10 +17448,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>580441</v>
+        <v>580421</v>
       </c>
       <c r="R150" t="n">
-        <v>7053267</v>
+        <v>7053299</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17483,7 +17483,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17520,7 +17520,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121126214</v>
+        <v>121126643</v>
       </c>
       <c r="B151" t="n">
         <v>78601</v>
@@ -17560,10 +17560,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>580564</v>
+        <v>580565</v>
       </c>
       <c r="R151" t="n">
-        <v>7053209</v>
+        <v>7053263</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17605,7 +17605,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17632,10 +17632,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121126027</v>
+        <v>121126530</v>
       </c>
       <c r="B152" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17648,44 +17648,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>580590</v>
+        <v>580571</v>
       </c>
       <c r="R152" t="n">
-        <v>7053152</v>
+        <v>7053237</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17717,7 +17707,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17727,7 +17717,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17754,10 +17744,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121125921</v>
+        <v>121127278</v>
       </c>
       <c r="B153" t="n">
-        <v>57351</v>
+        <v>90662</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17766,48 +17756,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>580600</v>
+        <v>580510</v>
       </c>
       <c r="R153" t="n">
-        <v>7053106</v>
+        <v>7053247</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17839,7 +17819,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17849,7 +17829,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17876,10 +17856,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121128951</v>
+        <v>121126972</v>
       </c>
       <c r="B154" t="n">
-        <v>79682</v>
+        <v>82385</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17892,21 +17872,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17916,10 +17896,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>580424</v>
+        <v>580535</v>
       </c>
       <c r="R154" t="n">
-        <v>7053312</v>
+        <v>7053234</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17951,7 +17931,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17961,7 +17941,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17988,10 +17968,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121127289</v>
+        <v>121127030</v>
       </c>
       <c r="B155" t="n">
-        <v>95375</v>
+        <v>78601</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18000,25 +17980,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18028,10 +18008,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>580508</v>
+        <v>580528</v>
       </c>
       <c r="R155" t="n">
-        <v>7053256</v>
+        <v>7053255</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18063,7 +18043,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18073,7 +18053,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18100,10 +18080,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121126530</v>
+        <v>121125921</v>
       </c>
       <c r="B156" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18116,34 +18096,44 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>580571</v>
+        <v>580600</v>
       </c>
       <c r="R156" t="n">
-        <v>7053237</v>
+        <v>7053106</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18175,7 +18165,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18185,7 +18175,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18212,10 +18202,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121126868</v>
+        <v>121127289</v>
       </c>
       <c r="B157" t="n">
-        <v>91089</v>
+        <v>95375</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18224,20 +18214,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6040162</v>
+        <v>2869</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18247,10 +18242,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>580542</v>
+        <v>580508</v>
       </c>
       <c r="R157" t="n">
-        <v>7053234</v>
+        <v>7053256</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18282,7 +18277,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18292,7 +18287,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18307,22 +18302,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121126972</v>
+        <v>121126868</v>
       </c>
       <c r="B158" t="n">
-        <v>82385</v>
+        <v>91089</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18335,21 +18330,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18359,7 +18349,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>580535</v>
+        <v>580542</v>
       </c>
       <c r="R158" t="n">
         <v>7053234</v>
@@ -18394,7 +18384,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18404,7 +18394,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18419,22 +18409,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121127803</v>
+        <v>121128951</v>
       </c>
       <c r="B159" t="n">
-        <v>56563</v>
+        <v>79682</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18443,43 +18433,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>580418</v>
+        <v>580424</v>
       </c>
       <c r="R159" t="n">
-        <v>7053258</v>
+        <v>7053312</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18511,7 +18496,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18521,7 +18506,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18548,10 +18533,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121126610</v>
+        <v>121127803</v>
       </c>
       <c r="B160" t="n">
-        <v>98081</v>
+        <v>56563</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18560,30 +18545,31 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -18592,10 +18578,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>580564</v>
+        <v>580418</v>
       </c>
       <c r="R160" t="n">
-        <v>7053248</v>
+        <v>7053258</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18627,7 +18613,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18637,7 +18623,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18652,22 +18638,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121126643</v>
+        <v>121126694</v>
       </c>
       <c r="B161" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18676,28 +18662,32 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
@@ -18739,7 +18729,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18749,7 +18739,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18776,10 +18766,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121126694</v>
+        <v>121127564</v>
       </c>
       <c r="B162" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18788,42 +18778,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>580565</v>
+        <v>580441</v>
       </c>
       <c r="R162" t="n">
-        <v>7053263</v>
+        <v>7053267</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18855,7 +18841,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18865,7 +18851,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18892,10 +18878,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121126779</v>
+        <v>121127610</v>
       </c>
       <c r="B163" t="n">
-        <v>78601</v>
+        <v>91973</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18904,25 +18890,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18932,10 +18918,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>580548</v>
+        <v>580433</v>
       </c>
       <c r="R163" t="n">
-        <v>7053237</v>
+        <v>7053267</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18967,7 +18953,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18977,7 +18963,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19004,10 +18990,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121127610</v>
+        <v>121126027</v>
       </c>
       <c r="B164" t="n">
-        <v>91973</v>
+        <v>57351</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19016,38 +19002,48 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>580433</v>
+        <v>580590</v>
       </c>
       <c r="R164" t="n">
-        <v>7053267</v>
+        <v>7053152</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19079,7 +19075,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19089,7 +19085,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19116,10 +19112,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121126876</v>
+        <v>121126610</v>
       </c>
       <c r="B165" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19128,38 +19124,42 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>580540</v>
+        <v>580564</v>
       </c>
       <c r="R165" t="n">
-        <v>7053257</v>
+        <v>7053248</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19216,22 +19216,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121125943</v>
+        <v>121126181</v>
       </c>
       <c r="B166" t="n">
-        <v>98081</v>
+        <v>95375</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19240,25 +19240,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>580603</v>
+        <v>580568</v>
       </c>
       <c r="R166" t="n">
-        <v>7053117</v>
+        <v>7053195</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19303,7 +19303,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19340,10 +19340,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121127710</v>
+        <v>121126876</v>
       </c>
       <c r="B167" t="n">
-        <v>91965</v>
+        <v>78601</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19356,21 +19356,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -19380,10 +19380,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>580426</v>
+        <v>580540</v>
       </c>
       <c r="R167" t="n">
-        <v>7053263</v>
+        <v>7053257</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -18990,10 +18990,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121126027</v>
+        <v>121126610</v>
       </c>
       <c r="B164" t="n">
-        <v>57351</v>
+        <v>98081</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19002,36 +19002,30 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -19040,10 +19034,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>580590</v>
+        <v>580564</v>
       </c>
       <c r="R164" t="n">
-        <v>7053152</v>
+        <v>7053248</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19075,7 +19069,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19085,7 +19079,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19100,22 +19094,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121126610</v>
+        <v>121126027</v>
       </c>
       <c r="B165" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19124,30 +19118,36 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -19156,10 +19156,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>580564</v>
+        <v>580590</v>
       </c>
       <c r="R165" t="n">
-        <v>7053248</v>
+        <v>7053152</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19216,12 +19216,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -16739,7 +16739,7 @@
         <v>121127710</v>
       </c>
       <c r="B144" t="n">
-        <v>91965</v>
+        <v>91977</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121129017</v>
+        <v>121125921</v>
       </c>
       <c r="B145" t="n">
-        <v>91973</v>
+        <v>57351</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16860,38 +16860,48 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>580426</v>
+        <v>580600</v>
       </c>
       <c r="R145" t="n">
-        <v>7053283</v>
+        <v>7053106</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16923,7 +16933,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16933,7 +16943,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16960,10 +16970,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121128867</v>
+        <v>121126972</v>
       </c>
       <c r="B146" t="n">
-        <v>95375</v>
+        <v>82388</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16972,25 +16982,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17000,10 +17010,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>580445</v>
+        <v>580535</v>
       </c>
       <c r="R146" t="n">
-        <v>7053311</v>
+        <v>7053234</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17035,7 +17045,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17045,7 +17055,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17072,10 +17082,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121126214</v>
+        <v>121126876</v>
       </c>
       <c r="B147" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17112,10 +17122,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>580564</v>
+        <v>580540</v>
       </c>
       <c r="R147" t="n">
-        <v>7053209</v>
+        <v>7053257</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17147,7 +17157,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17157,7 +17167,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17184,10 +17194,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121125943</v>
+        <v>121126530</v>
       </c>
       <c r="B148" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17196,25 +17206,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17224,10 +17234,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>580603</v>
+        <v>580571</v>
       </c>
       <c r="R148" t="n">
-        <v>7053117</v>
+        <v>7053237</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17259,7 +17269,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17269,7 +17279,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17296,10 +17306,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121126779</v>
+        <v>121126027</v>
       </c>
       <c r="B149" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17312,34 +17322,44 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>580548</v>
+        <v>580590</v>
       </c>
       <c r="R149" t="n">
-        <v>7053237</v>
+        <v>7053152</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17371,7 +17391,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17381,7 +17401,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17408,10 +17428,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121129042</v>
+        <v>121129017</v>
       </c>
       <c r="B150" t="n">
-        <v>91965</v>
+        <v>91985</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17420,25 +17440,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17448,10 +17468,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>580421</v>
+        <v>580426</v>
       </c>
       <c r="R150" t="n">
-        <v>7053299</v>
+        <v>7053283</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17483,7 +17503,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17493,7 +17513,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17520,10 +17540,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121126643</v>
+        <v>121128951</v>
       </c>
       <c r="B151" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17536,21 +17556,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17560,10 +17580,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>580565</v>
+        <v>580424</v>
       </c>
       <c r="R151" t="n">
-        <v>7053263</v>
+        <v>7053312</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17595,7 +17615,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17605,7 +17625,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17632,10 +17652,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121126530</v>
+        <v>121127289</v>
       </c>
       <c r="B152" t="n">
-        <v>78601</v>
+        <v>95388</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17644,25 +17664,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17672,10 +17692,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>580571</v>
+        <v>580508</v>
       </c>
       <c r="R152" t="n">
-        <v>7053237</v>
+        <v>7053256</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17707,7 +17727,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17717,7 +17737,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17744,10 +17764,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121127278</v>
+        <v>121127030</v>
       </c>
       <c r="B153" t="n">
-        <v>90662</v>
+        <v>78604</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17756,25 +17776,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17784,10 +17804,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>580510</v>
+        <v>580528</v>
       </c>
       <c r="R153" t="n">
-        <v>7053247</v>
+        <v>7053255</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17819,7 +17839,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17829,7 +17849,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17856,10 +17876,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121126972</v>
+        <v>121126868</v>
       </c>
       <c r="B154" t="n">
-        <v>82385</v>
+        <v>91101</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17872,21 +17892,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17896,7 +17911,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>580535</v>
+        <v>580542</v>
       </c>
       <c r="R154" t="n">
         <v>7053234</v>
@@ -17931,7 +17946,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17941,7 +17956,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17956,22 +17971,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121127030</v>
+        <v>121128867</v>
       </c>
       <c r="B155" t="n">
-        <v>78601</v>
+        <v>95388</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17980,25 +17995,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18008,10 +18023,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>580528</v>
+        <v>580445</v>
       </c>
       <c r="R155" t="n">
-        <v>7053255</v>
+        <v>7053311</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18043,7 +18058,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18053,7 +18068,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18080,10 +18095,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121125921</v>
+        <v>121126610</v>
       </c>
       <c r="B156" t="n">
-        <v>57351</v>
+        <v>98094</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18092,36 +18107,30 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -18130,10 +18139,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>580600</v>
+        <v>580564</v>
       </c>
       <c r="R156" t="n">
-        <v>7053106</v>
+        <v>7053248</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18165,7 +18174,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18175,7 +18184,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18190,22 +18199,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121127289</v>
+        <v>121127803</v>
       </c>
       <c r="B157" t="n">
-        <v>95375</v>
+        <v>56563</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18218,34 +18227,39 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2869</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>580508</v>
+        <v>580418</v>
       </c>
       <c r="R157" t="n">
-        <v>7053256</v>
+        <v>7053258</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18277,7 +18291,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18287,7 +18301,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18314,10 +18328,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121126868</v>
+        <v>121125943</v>
       </c>
       <c r="B158" t="n">
-        <v>91089</v>
+        <v>98094</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18326,20 +18340,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6040162</v>
+        <v>220787</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18349,10 +18368,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>580542</v>
+        <v>580603</v>
       </c>
       <c r="R158" t="n">
-        <v>7053234</v>
+        <v>7053117</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18384,7 +18403,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18394,7 +18413,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18409,22 +18428,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121128951</v>
+        <v>121127564</v>
       </c>
       <c r="B159" t="n">
-        <v>79682</v>
+        <v>91985</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18433,25 +18452,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18461,10 +18480,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>580424</v>
+        <v>580441</v>
       </c>
       <c r="R159" t="n">
-        <v>7053312</v>
+        <v>7053267</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18496,7 +18515,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18506,7 +18525,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18533,10 +18552,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121127803</v>
+        <v>121127610</v>
       </c>
       <c r="B160" t="n">
-        <v>56563</v>
+        <v>91985</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18549,39 +18568,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>580418</v>
+        <v>580433</v>
       </c>
       <c r="R160" t="n">
-        <v>7053258</v>
+        <v>7053267</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18613,7 +18627,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18623,7 +18637,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18650,10 +18664,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121126694</v>
+        <v>121126181</v>
       </c>
       <c r="B161" t="n">
-        <v>98081</v>
+        <v>95388</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18662,42 +18676,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>580565</v>
+        <v>580568</v>
       </c>
       <c r="R161" t="n">
-        <v>7053263</v>
+        <v>7053195</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18729,7 +18739,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18739,7 +18749,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18766,10 +18776,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121127564</v>
+        <v>121126214</v>
       </c>
       <c r="B162" t="n">
-        <v>91973</v>
+        <v>78604</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18778,25 +18788,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18806,10 +18816,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>580441</v>
+        <v>580564</v>
       </c>
       <c r="R162" t="n">
-        <v>7053267</v>
+        <v>7053209</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18841,7 +18851,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18851,7 +18861,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18878,10 +18888,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121127610</v>
+        <v>121127278</v>
       </c>
       <c r="B163" t="n">
-        <v>91973</v>
+        <v>90674</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18894,21 +18904,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18918,10 +18928,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>580433</v>
+        <v>580510</v>
       </c>
       <c r="R163" t="n">
-        <v>7053267</v>
+        <v>7053247</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18953,7 +18963,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18963,7 +18973,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18990,10 +19000,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121126610</v>
+        <v>121129042</v>
       </c>
       <c r="B164" t="n">
-        <v>98081</v>
+        <v>91977</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19002,42 +19012,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>580564</v>
+        <v>580421</v>
       </c>
       <c r="R164" t="n">
-        <v>7053248</v>
+        <v>7053299</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19069,7 +19075,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19079,7 +19085,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19094,22 +19100,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121126027</v>
+        <v>121126694</v>
       </c>
       <c r="B165" t="n">
-        <v>57351</v>
+        <v>98094</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19118,36 +19124,30 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -19156,10 +19156,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>580590</v>
+        <v>580565</v>
       </c>
       <c r="R165" t="n">
-        <v>7053152</v>
+        <v>7053263</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19228,10 +19228,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121126181</v>
+        <v>121126779</v>
       </c>
       <c r="B166" t="n">
-        <v>95375</v>
+        <v>78604</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19240,25 +19240,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>580568</v>
+        <v>580548</v>
       </c>
       <c r="R166" t="n">
-        <v>7053195</v>
+        <v>7053237</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19303,7 +19303,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19340,10 +19340,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121126876</v>
+        <v>121126643</v>
       </c>
       <c r="B167" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19380,10 +19380,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>580540</v>
+        <v>580565</v>
       </c>
       <c r="R167" t="n">
-        <v>7053257</v>
+        <v>7053263</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -16736,10 +16736,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121127710</v>
+        <v>121125943</v>
       </c>
       <c r="B144" t="n">
-        <v>91977</v>
+        <v>98095</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16748,25 +16748,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16776,10 +16776,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>580426</v>
+        <v>580603</v>
       </c>
       <c r="R144" t="n">
-        <v>7053263</v>
+        <v>7053117</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16848,10 +16848,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121125921</v>
+        <v>121127610</v>
       </c>
       <c r="B145" t="n">
-        <v>57351</v>
+        <v>91986</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16860,48 +16860,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>580600</v>
+        <v>580433</v>
       </c>
       <c r="R145" t="n">
-        <v>7053106</v>
+        <v>7053267</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16933,7 +16923,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16943,7 +16933,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16970,10 +16960,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121126972</v>
+        <v>121127030</v>
       </c>
       <c r="B146" t="n">
-        <v>82388</v>
+        <v>78604</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16986,21 +16976,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17010,10 +17000,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>580535</v>
+        <v>580528</v>
       </c>
       <c r="R146" t="n">
-        <v>7053234</v>
+        <v>7053255</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17045,7 +17035,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17055,7 +17045,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17082,7 +17072,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121126876</v>
+        <v>121126530</v>
       </c>
       <c r="B147" t="n">
         <v>78604</v>
@@ -17122,10 +17112,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>580540</v>
+        <v>580571</v>
       </c>
       <c r="R147" t="n">
-        <v>7053257</v>
+        <v>7053237</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17157,7 +17147,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17167,7 +17157,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17194,10 +17184,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121126530</v>
+        <v>121129042</v>
       </c>
       <c r="B148" t="n">
-        <v>78604</v>
+        <v>91978</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17210,21 +17200,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17234,10 +17224,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>580571</v>
+        <v>580421</v>
       </c>
       <c r="R148" t="n">
-        <v>7053237</v>
+        <v>7053299</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17269,7 +17259,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17279,7 +17269,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17306,10 +17296,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121126027</v>
+        <v>121126868</v>
       </c>
       <c r="B149" t="n">
-        <v>57351</v>
+        <v>91102</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17322,44 +17312,29 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>580590</v>
+        <v>580542</v>
       </c>
       <c r="R149" t="n">
-        <v>7053152</v>
+        <v>7053234</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17391,7 +17366,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17401,7 +17376,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17416,22 +17391,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121129017</v>
+        <v>121127289</v>
       </c>
       <c r="B150" t="n">
-        <v>91985</v>
+        <v>95389</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17444,21 +17419,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17468,10 +17443,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>580426</v>
+        <v>580508</v>
       </c>
       <c r="R150" t="n">
-        <v>7053283</v>
+        <v>7053256</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17503,7 +17478,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17513,7 +17488,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17540,10 +17515,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121128951</v>
+        <v>121126643</v>
       </c>
       <c r="B151" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17556,21 +17531,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17580,10 +17555,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>580424</v>
+        <v>580565</v>
       </c>
       <c r="R151" t="n">
-        <v>7053312</v>
+        <v>7053263</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17615,7 +17590,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17625,7 +17600,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17652,10 +17627,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121127289</v>
+        <v>121125921</v>
       </c>
       <c r="B152" t="n">
-        <v>95388</v>
+        <v>57351</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17664,38 +17639,48 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>580508</v>
+        <v>580600</v>
       </c>
       <c r="R152" t="n">
-        <v>7053256</v>
+        <v>7053106</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17727,7 +17712,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17737,7 +17722,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17764,10 +17749,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121127030</v>
+        <v>121126610</v>
       </c>
       <c r="B153" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17776,38 +17761,42 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>580528</v>
+        <v>580564</v>
       </c>
       <c r="R153" t="n">
-        <v>7053255</v>
+        <v>7053248</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17839,7 +17828,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17849,7 +17838,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17864,22 +17853,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121126868</v>
+        <v>121126779</v>
       </c>
       <c r="B154" t="n">
-        <v>91101</v>
+        <v>78604</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17892,16 +17881,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6040162</v>
+        <v>6425</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17911,10 +17905,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>580542</v>
+        <v>580548</v>
       </c>
       <c r="R154" t="n">
-        <v>7053234</v>
+        <v>7053237</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17946,7 +17940,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17956,7 +17950,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17971,22 +17965,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121128867</v>
+        <v>121128951</v>
       </c>
       <c r="B155" t="n">
-        <v>95388</v>
+        <v>79685</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17995,25 +17989,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18023,10 +18017,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>580445</v>
+        <v>580424</v>
       </c>
       <c r="R155" t="n">
-        <v>7053311</v>
+        <v>7053312</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18058,7 +18052,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18068,7 +18062,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18095,10 +18089,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121126610</v>
+        <v>121126027</v>
       </c>
       <c r="B156" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18107,30 +18101,36 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -18139,10 +18139,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>580564</v>
+        <v>580590</v>
       </c>
       <c r="R156" t="n">
-        <v>7053248</v>
+        <v>7053152</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18174,7 +18174,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18199,22 +18199,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121127803</v>
+        <v>121128867</v>
       </c>
       <c r="B157" t="n">
-        <v>56563</v>
+        <v>95389</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18227,39 +18227,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100138</v>
+        <v>2869</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>580418</v>
+        <v>580445</v>
       </c>
       <c r="R157" t="n">
-        <v>7053258</v>
+        <v>7053311</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18291,7 +18286,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18301,7 +18296,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18328,10 +18323,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121125943</v>
+        <v>121127564</v>
       </c>
       <c r="B158" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18340,25 +18335,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18368,10 +18363,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>580603</v>
+        <v>580441</v>
       </c>
       <c r="R158" t="n">
-        <v>7053117</v>
+        <v>7053267</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18403,7 +18398,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18413,7 +18408,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18440,10 +18435,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121127564</v>
+        <v>121126694</v>
       </c>
       <c r="B159" t="n">
-        <v>91985</v>
+        <v>98095</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18452,38 +18447,42 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>580441</v>
+        <v>580565</v>
       </c>
       <c r="R159" t="n">
-        <v>7053267</v>
+        <v>7053263</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18515,7 +18514,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18525,7 +18524,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18552,10 +18551,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121127610</v>
+        <v>121126876</v>
       </c>
       <c r="B160" t="n">
-        <v>91985</v>
+        <v>78604</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18564,25 +18563,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18592,10 +18591,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>580433</v>
+        <v>580540</v>
       </c>
       <c r="R160" t="n">
-        <v>7053267</v>
+        <v>7053257</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18627,7 +18626,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18637,7 +18636,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18664,10 +18663,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121126181</v>
+        <v>121127278</v>
       </c>
       <c r="B161" t="n">
-        <v>95388</v>
+        <v>90675</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18680,21 +18679,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18704,10 +18703,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>580568</v>
+        <v>580510</v>
       </c>
       <c r="R161" t="n">
-        <v>7053195</v>
+        <v>7053247</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18739,7 +18738,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18749,7 +18748,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18776,10 +18775,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121126214</v>
+        <v>121127803</v>
       </c>
       <c r="B162" t="n">
-        <v>78604</v>
+        <v>56563</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18788,38 +18787,43 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>580564</v>
+        <v>580418</v>
       </c>
       <c r="R162" t="n">
-        <v>7053209</v>
+        <v>7053258</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18851,7 +18855,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18861,7 +18865,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18888,10 +18892,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121127278</v>
+        <v>121129017</v>
       </c>
       <c r="B163" t="n">
-        <v>90674</v>
+        <v>91986</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18904,21 +18908,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18928,10 +18932,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>580510</v>
+        <v>580426</v>
       </c>
       <c r="R163" t="n">
-        <v>7053247</v>
+        <v>7053283</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18963,7 +18967,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18973,7 +18977,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19000,10 +19004,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121129042</v>
+        <v>121126972</v>
       </c>
       <c r="B164" t="n">
-        <v>91977</v>
+        <v>82388</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19016,21 +19020,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4361</v>
+        <v>1312</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19040,10 +19044,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>580421</v>
+        <v>580535</v>
       </c>
       <c r="R164" t="n">
-        <v>7053299</v>
+        <v>7053234</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19075,7 +19079,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19085,7 +19089,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19112,10 +19116,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121126694</v>
+        <v>121127710</v>
       </c>
       <c r="B165" t="n">
-        <v>98094</v>
+        <v>91978</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19124,39 +19128,35 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>580565</v>
+        <v>580426</v>
       </c>
       <c r="R165" t="n">
         <v>7053263</v>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19228,7 +19228,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121126779</v>
+        <v>121126214</v>
       </c>
       <c r="B166" t="n">
         <v>78604</v>
@@ -19268,10 +19268,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>580548</v>
+        <v>580564</v>
       </c>
       <c r="R166" t="n">
-        <v>7053237</v>
+        <v>7053209</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19303,7 +19303,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19340,10 +19340,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121126643</v>
+        <v>121126181</v>
       </c>
       <c r="B167" t="n">
-        <v>78604</v>
+        <v>95389</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19352,25 +19352,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -19380,10 +19380,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>580565</v>
+        <v>580568</v>
       </c>
       <c r="R167" t="n">
-        <v>7053263</v>
+        <v>7053195</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -16736,10 +16736,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121125943</v>
+        <v>121127610</v>
       </c>
       <c r="B144" t="n">
-        <v>98095</v>
+        <v>91989</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16748,25 +16748,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16776,10 +16776,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>580603</v>
+        <v>580433</v>
       </c>
       <c r="R144" t="n">
-        <v>7053117</v>
+        <v>7053267</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16848,10 +16848,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121127610</v>
+        <v>121129042</v>
       </c>
       <c r="B145" t="n">
-        <v>91986</v>
+        <v>91981</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16860,25 +16860,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16888,10 +16888,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>580433</v>
+        <v>580421</v>
       </c>
       <c r="R145" t="n">
-        <v>7053267</v>
+        <v>7053299</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16960,10 +16960,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121127030</v>
+        <v>121128951</v>
       </c>
       <c r="B146" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16976,21 +16976,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17000,10 +17000,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>580528</v>
+        <v>580424</v>
       </c>
       <c r="R146" t="n">
-        <v>7053255</v>
+        <v>7053312</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17072,10 +17072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121126530</v>
+        <v>121129017</v>
       </c>
       <c r="B147" t="n">
-        <v>78604</v>
+        <v>91989</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17084,25 +17084,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17112,10 +17112,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>580571</v>
+        <v>580426</v>
       </c>
       <c r="R147" t="n">
-        <v>7053237</v>
+        <v>7053283</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17184,10 +17184,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121129042</v>
+        <v>121127710</v>
       </c>
       <c r="B148" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17224,10 +17224,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>580421</v>
+        <v>580426</v>
       </c>
       <c r="R148" t="n">
-        <v>7053299</v>
+        <v>7053263</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17296,10 +17296,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121126868</v>
+        <v>121126027</v>
       </c>
       <c r="B149" t="n">
-        <v>91102</v>
+        <v>57354</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17312,29 +17312,44 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6040162</v>
+        <v>100109</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>580542</v>
+        <v>580590</v>
       </c>
       <c r="R149" t="n">
-        <v>7053234</v>
+        <v>7053152</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17366,7 +17381,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17376,7 +17391,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17391,22 +17406,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121127289</v>
+        <v>121128867</v>
       </c>
       <c r="B150" t="n">
-        <v>95389</v>
+        <v>95392</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17443,10 +17458,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>580508</v>
+        <v>580445</v>
       </c>
       <c r="R150" t="n">
-        <v>7053256</v>
+        <v>7053311</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17478,7 +17493,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17488,7 +17503,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17515,10 +17530,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121126643</v>
+        <v>121127278</v>
       </c>
       <c r="B151" t="n">
-        <v>78604</v>
+        <v>90678</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17527,25 +17542,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17555,10 +17570,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>580565</v>
+        <v>580510</v>
       </c>
       <c r="R151" t="n">
-        <v>7053263</v>
+        <v>7053247</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17590,7 +17605,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17600,7 +17615,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17627,10 +17642,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121125921</v>
+        <v>121127564</v>
       </c>
       <c r="B152" t="n">
-        <v>57351</v>
+        <v>91989</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17639,48 +17654,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>580600</v>
+        <v>580441</v>
       </c>
       <c r="R152" t="n">
-        <v>7053106</v>
+        <v>7053267</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17712,7 +17717,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17722,7 +17727,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17749,10 +17754,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121126610</v>
+        <v>121126694</v>
       </c>
       <c r="B153" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17784,7 +17789,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -17793,10 +17798,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>580564</v>
+        <v>580565</v>
       </c>
       <c r="R153" t="n">
-        <v>7053248</v>
+        <v>7053263</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17828,7 +17833,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17838,7 +17843,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17853,22 +17858,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121126779</v>
+        <v>121126868</v>
       </c>
       <c r="B154" t="n">
-        <v>78604</v>
+        <v>91105</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17881,21 +17886,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17905,10 +17905,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>580548</v>
+        <v>580542</v>
       </c>
       <c r="R154" t="n">
-        <v>7053237</v>
+        <v>7053234</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17950,7 +17950,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17965,22 +17965,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121128951</v>
+        <v>121126779</v>
       </c>
       <c r="B155" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17993,21 +17993,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -18017,10 +18017,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>580424</v>
+        <v>580548</v>
       </c>
       <c r="R155" t="n">
-        <v>7053312</v>
+        <v>7053237</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18052,7 +18052,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18089,10 +18089,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121126027</v>
+        <v>121127289</v>
       </c>
       <c r="B156" t="n">
-        <v>57351</v>
+        <v>95392</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18101,48 +18101,38 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>580590</v>
+        <v>580508</v>
       </c>
       <c r="R156" t="n">
-        <v>7053152</v>
+        <v>7053256</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18174,7 +18164,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18184,7 +18174,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18211,10 +18201,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121128867</v>
+        <v>121126643</v>
       </c>
       <c r="B157" t="n">
-        <v>95389</v>
+        <v>78607</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18223,25 +18213,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18251,10 +18241,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>580445</v>
+        <v>580565</v>
       </c>
       <c r="R157" t="n">
-        <v>7053311</v>
+        <v>7053263</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18286,7 +18276,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18296,7 +18286,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18323,10 +18313,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121127564</v>
+        <v>121126876</v>
       </c>
       <c r="B158" t="n">
-        <v>91986</v>
+        <v>78607</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18335,25 +18325,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18363,10 +18353,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>580441</v>
+        <v>580540</v>
       </c>
       <c r="R158" t="n">
-        <v>7053267</v>
+        <v>7053257</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18398,7 +18388,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18408,7 +18398,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18435,10 +18425,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121126694</v>
+        <v>121127030</v>
       </c>
       <c r="B159" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18447,42 +18437,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>580565</v>
+        <v>580528</v>
       </c>
       <c r="R159" t="n">
-        <v>7053263</v>
+        <v>7053255</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18514,7 +18500,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18524,7 +18510,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18551,10 +18537,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121126876</v>
+        <v>121126214</v>
       </c>
       <c r="B160" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18591,10 +18577,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>580540</v>
+        <v>580564</v>
       </c>
       <c r="R160" t="n">
-        <v>7053257</v>
+        <v>7053209</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18626,7 +18612,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18636,7 +18622,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18663,10 +18649,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121127278</v>
+        <v>121126530</v>
       </c>
       <c r="B161" t="n">
-        <v>90675</v>
+        <v>78607</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18675,25 +18661,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18703,10 +18689,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>580510</v>
+        <v>580571</v>
       </c>
       <c r="R161" t="n">
-        <v>7053247</v>
+        <v>7053237</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18738,7 +18724,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18748,7 +18734,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18778,7 +18764,7 @@
         <v>121127803</v>
       </c>
       <c r="B162" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18892,10 +18878,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121129017</v>
+        <v>121126181</v>
       </c>
       <c r="B163" t="n">
-        <v>91986</v>
+        <v>95392</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18908,21 +18894,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18932,10 +18918,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>580426</v>
+        <v>580568</v>
       </c>
       <c r="R163" t="n">
-        <v>7053283</v>
+        <v>7053195</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18967,7 +18953,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18977,7 +18963,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19007,7 +18993,7 @@
         <v>121126972</v>
       </c>
       <c r="B164" t="n">
-        <v>82388</v>
+        <v>82391</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19116,10 +19102,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121127710</v>
+        <v>121125943</v>
       </c>
       <c r="B165" t="n">
-        <v>91978</v>
+        <v>98098</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19128,25 +19114,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19156,10 +19142,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>580426</v>
+        <v>580603</v>
       </c>
       <c r="R165" t="n">
-        <v>7053263</v>
+        <v>7053117</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19191,7 +19177,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19201,7 +19187,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19228,10 +19214,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121126214</v>
+        <v>121126610</v>
       </c>
       <c r="B166" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19240,28 +19226,32 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
@@ -19271,7 +19261,7 @@
         <v>580564</v>
       </c>
       <c r="R166" t="n">
-        <v>7053209</v>
+        <v>7053248</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19303,7 +19293,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19313,7 +19303,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19328,22 +19318,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121126181</v>
+        <v>121125921</v>
       </c>
       <c r="B167" t="n">
-        <v>95389</v>
+        <v>57354</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19352,38 +19342,48 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>580568</v>
+        <v>580600</v>
       </c>
       <c r="R167" t="n">
-        <v>7053195</v>
+        <v>7053106</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -16736,10 +16736,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121127610</v>
+        <v>121126181</v>
       </c>
       <c r="B144" t="n">
-        <v>91989</v>
+        <v>95392</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16752,21 +16752,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16776,10 +16776,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>580433</v>
+        <v>580568</v>
       </c>
       <c r="R144" t="n">
-        <v>7053267</v>
+        <v>7053195</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16811,7 +16811,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16821,7 +16821,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16848,10 +16848,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121129042</v>
+        <v>121126214</v>
       </c>
       <c r="B145" t="n">
-        <v>91981</v>
+        <v>78607</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16864,21 +16864,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16888,10 +16888,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>580421</v>
+        <v>580564</v>
       </c>
       <c r="R145" t="n">
-        <v>7053299</v>
+        <v>7053209</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16933,7 +16933,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16960,10 +16960,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121128951</v>
+        <v>121127030</v>
       </c>
       <c r="B146" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16976,21 +16976,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17000,10 +17000,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>580424</v>
+        <v>580528</v>
       </c>
       <c r="R146" t="n">
-        <v>7053312</v>
+        <v>7053255</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17072,10 +17072,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121129017</v>
+        <v>121127278</v>
       </c>
       <c r="B147" t="n">
-        <v>91989</v>
+        <v>90678</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17088,21 +17088,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17112,10 +17112,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>580426</v>
+        <v>580510</v>
       </c>
       <c r="R147" t="n">
-        <v>7053283</v>
+        <v>7053247</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17184,10 +17184,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121127710</v>
+        <v>121126868</v>
       </c>
       <c r="B148" t="n">
-        <v>91981</v>
+        <v>91105</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17200,21 +17200,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17224,10 +17219,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>580426</v>
+        <v>580542</v>
       </c>
       <c r="R148" t="n">
-        <v>7053263</v>
+        <v>7053234</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17259,7 +17254,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17269,7 +17264,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17284,22 +17279,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121126027</v>
+        <v>121127610</v>
       </c>
       <c r="B149" t="n">
-        <v>57354</v>
+        <v>91989</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17308,48 +17303,38 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>580590</v>
+        <v>580433</v>
       </c>
       <c r="R149" t="n">
-        <v>7053152</v>
+        <v>7053267</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17381,7 +17366,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17391,7 +17376,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17418,10 +17403,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121128867</v>
+        <v>121126027</v>
       </c>
       <c r="B150" t="n">
-        <v>95392</v>
+        <v>57354</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17430,38 +17415,48 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>580445</v>
+        <v>580590</v>
       </c>
       <c r="R150" t="n">
-        <v>7053311</v>
+        <v>7053152</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17493,7 +17488,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17503,7 +17498,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17530,10 +17525,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121127278</v>
+        <v>121127803</v>
       </c>
       <c r="B151" t="n">
-        <v>90678</v>
+        <v>56566</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17546,34 +17541,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>580510</v>
+        <v>580418</v>
       </c>
       <c r="R151" t="n">
-        <v>7053247</v>
+        <v>7053258</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17605,7 +17605,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17615,7 +17615,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17642,10 +17642,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121127564</v>
+        <v>121129042</v>
       </c>
       <c r="B152" t="n">
-        <v>91989</v>
+        <v>91981</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17654,25 +17654,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17682,10 +17682,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>580441</v>
+        <v>580421</v>
       </c>
       <c r="R152" t="n">
-        <v>7053267</v>
+        <v>7053299</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17754,7 +17754,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121126694</v>
+        <v>121126610</v>
       </c>
       <c r="B153" t="n">
         <v>98098</v>
@@ -17789,7 +17789,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -17798,10 +17798,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>580565</v>
+        <v>580564</v>
       </c>
       <c r="R153" t="n">
-        <v>7053263</v>
+        <v>7053248</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17858,22 +17858,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121126868</v>
+        <v>121127710</v>
       </c>
       <c r="B154" t="n">
-        <v>91105</v>
+        <v>91981</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17886,16 +17886,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6040162</v>
+        <v>4361</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17905,10 +17910,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>580542</v>
+        <v>580426</v>
       </c>
       <c r="R154" t="n">
-        <v>7053234</v>
+        <v>7053263</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17940,7 +17945,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17950,7 +17955,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17965,19 +17970,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121126779</v>
+        <v>121126643</v>
       </c>
       <c r="B155" t="n">
         <v>78607</v>
@@ -18017,10 +18022,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>580548</v>
+        <v>580565</v>
       </c>
       <c r="R155" t="n">
-        <v>7053237</v>
+        <v>7053263</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18052,7 +18057,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18062,7 +18067,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18089,10 +18094,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121127289</v>
+        <v>121127564</v>
       </c>
       <c r="B156" t="n">
-        <v>95392</v>
+        <v>91989</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18105,21 +18110,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18129,10 +18134,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>580508</v>
+        <v>580441</v>
       </c>
       <c r="R156" t="n">
-        <v>7053256</v>
+        <v>7053267</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18164,7 +18169,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18174,7 +18179,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18201,10 +18206,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121126643</v>
+        <v>121125921</v>
       </c>
       <c r="B157" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18217,34 +18222,44 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>580565</v>
+        <v>580600</v>
       </c>
       <c r="R157" t="n">
-        <v>7053263</v>
+        <v>7053106</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18276,7 +18291,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18286,7 +18301,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18425,10 +18440,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121127030</v>
+        <v>121127289</v>
       </c>
       <c r="B159" t="n">
-        <v>78607</v>
+        <v>95392</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18437,25 +18452,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18465,10 +18480,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>580528</v>
+        <v>580508</v>
       </c>
       <c r="R159" t="n">
-        <v>7053255</v>
+        <v>7053256</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18500,7 +18515,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18510,7 +18525,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18537,10 +18552,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121126214</v>
+        <v>121126972</v>
       </c>
       <c r="B160" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18553,21 +18568,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18577,10 +18592,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>580564</v>
+        <v>580535</v>
       </c>
       <c r="R160" t="n">
-        <v>7053209</v>
+        <v>7053234</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18612,7 +18627,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18622,7 +18637,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18649,10 +18664,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121126530</v>
+        <v>121129017</v>
       </c>
       <c r="B161" t="n">
-        <v>78607</v>
+        <v>91989</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18661,25 +18676,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18689,10 +18704,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>580571</v>
+        <v>580426</v>
       </c>
       <c r="R161" t="n">
-        <v>7053237</v>
+        <v>7053283</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18724,7 +18739,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18734,7 +18749,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18761,10 +18776,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121127803</v>
+        <v>121125943</v>
       </c>
       <c r="B162" t="n">
-        <v>56566</v>
+        <v>98098</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18773,43 +18788,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>580418</v>
+        <v>580603</v>
       </c>
       <c r="R162" t="n">
-        <v>7053258</v>
+        <v>7053117</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18841,7 +18851,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18851,7 +18861,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18878,10 +18888,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121126181</v>
+        <v>121126530</v>
       </c>
       <c r="B163" t="n">
-        <v>95392</v>
+        <v>78607</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18890,25 +18900,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18918,10 +18928,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>580568</v>
+        <v>580571</v>
       </c>
       <c r="R163" t="n">
-        <v>7053195</v>
+        <v>7053237</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18953,7 +18963,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18963,7 +18973,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18990,10 +19000,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121126972</v>
+        <v>121126779</v>
       </c>
       <c r="B164" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19006,21 +19016,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19030,10 +19040,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>580535</v>
+        <v>580548</v>
       </c>
       <c r="R164" t="n">
-        <v>7053234</v>
+        <v>7053237</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19065,7 +19075,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19075,7 +19085,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19102,10 +19112,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121125943</v>
+        <v>121128867</v>
       </c>
       <c r="B165" t="n">
-        <v>98098</v>
+        <v>95392</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19114,25 +19124,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19142,10 +19152,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>580603</v>
+        <v>580445</v>
       </c>
       <c r="R165" t="n">
-        <v>7053117</v>
+        <v>7053311</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19177,7 +19187,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19187,7 +19197,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19214,10 +19224,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121126610</v>
+        <v>121128951</v>
       </c>
       <c r="B166" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19226,42 +19236,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>580564</v>
+        <v>580424</v>
       </c>
       <c r="R166" t="n">
-        <v>7053248</v>
+        <v>7053312</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19293,7 +19299,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19303,7 +19309,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19318,22 +19324,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121125921</v>
+        <v>121126694</v>
       </c>
       <c r="B167" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -19342,36 +19348,30 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -19380,10 +19380,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>580600</v>
+        <v>580565</v>
       </c>
       <c r="R167" t="n">
-        <v>7053106</v>
+        <v>7053263</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -15903,11 +15903,11 @@
         <v>120896287</v>
       </c>
       <c r="B136" t="n">
-        <v>91137</v>
+        <v>91168</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -15903,7 +15903,7 @@
         <v>120896287</v>
       </c>
       <c r="B136" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -15903,7 +15903,7 @@
         <v>120896287</v>
       </c>
       <c r="B136" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -15903,7 +15903,7 @@
         <v>120896287</v>
       </c>
       <c r="B136" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -15903,7 +15903,7 @@
         <v>120896287</v>
       </c>
       <c r="B136" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>

--- a/artfynd/A 59323-2021 artfynd.xlsx
+++ b/artfynd/A 59323-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY167"/>
+  <dimension ref="A1:AY165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7426,10 +7426,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>109675711</v>
+        <v>109677531</v>
       </c>
       <c r="B61" t="n">
-        <v>96334</v>
+        <v>78569</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7438,25 +7438,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580601.5977380262</v>
+        <v>580608.6254787064</v>
       </c>
       <c r="R61" t="n">
-        <v>7053137.972261772</v>
+        <v>7053142.158393887</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7539,10 +7539,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>109677531</v>
+        <v>109676259</v>
       </c>
       <c r="B62" t="n">
-        <v>78569</v>
+        <v>96334</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7551,28 +7551,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7580,10 +7584,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580608.6254787064</v>
+        <v>580592.7310835186</v>
       </c>
       <c r="R62" t="n">
-        <v>7053142.158393887</v>
+        <v>7053135.965868418</v>
       </c>
       <c r="S62" t="n">
         <v>2</v>
@@ -7615,7 +7619,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7625,7 +7629,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7652,10 +7656,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>109676259</v>
+        <v>109676299</v>
       </c>
       <c r="B63" t="n">
-        <v>96334</v>
+        <v>78569</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7664,32 +7668,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580592.7310835186</v>
+        <v>580591.7946810514</v>
       </c>
       <c r="R63" t="n">
-        <v>7053135.965868418</v>
+        <v>7053137.723233062</v>
       </c>
       <c r="S63" t="n">
         <v>2</v>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7769,7 +7769,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>109676299</v>
+        <v>109938142</v>
       </c>
       <c r="B64" t="n">
         <v>78569</v>
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>580591.7946810514</v>
+        <v>580582.8645727282</v>
       </c>
       <c r="R64" t="n">
-        <v>7053137.723233062</v>
+        <v>7053278.649437097</v>
       </c>
       <c r="S64" t="n">
         <v>2</v>
@@ -7840,22 +7840,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7882,10 +7882,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>109938142</v>
+        <v>109938226</v>
       </c>
       <c r="B65" t="n">
-        <v>78569</v>
+        <v>96334</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7894,28 +7894,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7923,10 +7927,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580582.8645727282</v>
+        <v>580564.7252208437</v>
       </c>
       <c r="R65" t="n">
-        <v>7053278.649437097</v>
+        <v>7053290.656218305</v>
       </c>
       <c r="S65" t="n">
         <v>2</v>
@@ -7958,7 +7962,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7968,7 +7972,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7995,7 +7999,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>109938226</v>
+        <v>109937707</v>
       </c>
       <c r="B66" t="n">
         <v>96334</v>
@@ -8030,7 +8034,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -8040,10 +8044,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>580564.7252208437</v>
+        <v>580586.624885697</v>
       </c>
       <c r="R66" t="n">
-        <v>7053290.656218305</v>
+        <v>7053200.822124994</v>
       </c>
       <c r="S66" t="n">
         <v>2</v>
@@ -8075,7 +8079,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8085,7 +8089,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8112,10 +8116,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>109937707</v>
+        <v>109938379</v>
       </c>
       <c r="B67" t="n">
-        <v>96334</v>
+        <v>78569</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8124,32 +8128,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>580586.624885697</v>
+        <v>580570.4885900728</v>
       </c>
       <c r="R67" t="n">
-        <v>7053200.822124994</v>
+        <v>7053309.503700823</v>
       </c>
       <c r="S67" t="n">
         <v>2</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8229,10 +8229,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>109938379</v>
+        <v>109937780</v>
       </c>
       <c r="B68" t="n">
-        <v>78569</v>
+        <v>96334</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8241,28 +8241,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8270,10 +8274,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>580570.4885900728</v>
+        <v>580581.5991284512</v>
       </c>
       <c r="R68" t="n">
-        <v>7053309.503700823</v>
+        <v>7053205.592533772</v>
       </c>
       <c r="S68" t="n">
         <v>2</v>
@@ -8305,7 +8309,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8315,7 +8319,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8342,10 +8346,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>109937780</v>
+        <v>109938082</v>
       </c>
       <c r="B69" t="n">
-        <v>96334</v>
+        <v>56395</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8354,43 +8358,44 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>580581.5991284512</v>
+        <v>580585.9044673922</v>
       </c>
       <c r="R69" t="n">
-        <v>7053205.592533772</v>
+        <v>7053281.843525951</v>
       </c>
       <c r="S69" t="n">
         <v>2</v>
@@ -8422,7 +8427,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8432,7 +8437,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8459,10 +8464,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>109938082</v>
+        <v>109938127</v>
       </c>
       <c r="B70" t="n">
-        <v>56395</v>
+        <v>96334</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8471,44 +8476,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>580585.9044673922</v>
+        <v>580582.8645727282</v>
       </c>
       <c r="R70" t="n">
-        <v>7053281.843525951</v>
+        <v>7053278.649437097</v>
       </c>
       <c r="S70" t="n">
         <v>2</v>
@@ -8540,7 +8544,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8550,7 +8554,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8577,7 +8581,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>109938127</v>
+        <v>109937280</v>
       </c>
       <c r="B71" t="n">
         <v>96334</v>
@@ -8612,7 +8616,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -8622,10 +8626,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>580582.8645727282</v>
+        <v>580601.4016923031</v>
       </c>
       <c r="R71" t="n">
-        <v>7053278.649437097</v>
+        <v>7053215.891666325</v>
       </c>
       <c r="S71" t="n">
         <v>2</v>
@@ -8657,7 +8661,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8667,7 +8671,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8694,7 +8698,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>109937280</v>
+        <v>109938637</v>
       </c>
       <c r="B72" t="n">
         <v>96334</v>
@@ -8729,7 +8733,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -8739,10 +8743,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>580601.4016923031</v>
+        <v>580582.3946341453</v>
       </c>
       <c r="R72" t="n">
-        <v>7053215.891666325</v>
+        <v>7053314.703990972</v>
       </c>
       <c r="S72" t="n">
         <v>2</v>
@@ -8774,7 +8778,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8784,7 +8788,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8811,10 +8815,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>109938637</v>
+        <v>109936547</v>
       </c>
       <c r="B73" t="n">
-        <v>96334</v>
+        <v>89832</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8827,28 +8831,24 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>580582.3946341453</v>
+        <v>580599.0400329558</v>
       </c>
       <c r="R73" t="n">
-        <v>7053314.703990972</v>
+        <v>7053185.997986676</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8928,10 +8928,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>109936547</v>
+        <v>111949591</v>
       </c>
       <c r="B74" t="n">
-        <v>89832</v>
+        <v>96735</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8944,35 +8944,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Slättesmyran, Ång</t>
+          <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>580599.0400329558</v>
+        <v>580476</v>
       </c>
       <c r="R74" t="n">
-        <v>7053185.997986676</v>
+        <v>7053321</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -8999,22 +9003,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9041,10 +9045,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>111949591</v>
+        <v>111950184</v>
       </c>
       <c r="B75" t="n">
-        <v>96735</v>
+        <v>56575</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9053,32 +9057,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9086,13 +9086,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580476</v>
+        <v>580447</v>
       </c>
       <c r="R75" t="n">
-        <v>7053321</v>
+        <v>7053302</v>
       </c>
       <c r="S75" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9158,10 +9158,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>111950184</v>
+        <v>111949317</v>
       </c>
       <c r="B76" t="n">
-        <v>56575</v>
+        <v>96652</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9170,25 +9170,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9199,13 +9199,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580447</v>
+        <v>580500</v>
       </c>
       <c r="R76" t="n">
-        <v>7053302</v>
+        <v>7053329</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9271,10 +9271,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>111949317</v>
+        <v>111949678</v>
       </c>
       <c r="B77" t="n">
-        <v>96652</v>
+        <v>96735</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9283,28 +9283,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9312,10 +9316,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580500</v>
+        <v>580467</v>
       </c>
       <c r="R77" t="n">
-        <v>7053329</v>
+        <v>7053330</v>
       </c>
       <c r="S77" t="n">
         <v>2</v>
@@ -9347,7 +9351,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9357,7 +9361,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9384,7 +9388,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>111949678</v>
+        <v>111949575</v>
       </c>
       <c r="B78" t="n">
         <v>96735</v>
@@ -9419,7 +9423,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -9429,13 +9438,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580467</v>
+        <v>580471</v>
       </c>
       <c r="R78" t="n">
-        <v>7053330</v>
+        <v>7053333</v>
       </c>
       <c r="S78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9464,7 +9473,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9474,7 +9483,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9489,61 +9498,52 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>111949575</v>
+        <v>112229883</v>
       </c>
       <c r="B79" t="n">
-        <v>96735</v>
+        <v>91599</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9551,13 +9551,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580471</v>
+        <v>580572</v>
       </c>
       <c r="R79" t="n">
-        <v>7053333</v>
+        <v>7053336</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9581,22 +9581,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9611,22 +9611,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112230127</v>
+        <v>114564259</v>
       </c>
       <c r="B80" t="n">
-        <v>56461</v>
+        <v>57265</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9669,13 +9669,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580465</v>
+        <v>580489</v>
       </c>
       <c r="R80" t="n">
-        <v>7053325</v>
+        <v>7053227</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9699,22 +9699,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9741,14 +9741,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112229883</v>
+        <v>114564122</v>
       </c>
       <c r="B81" t="n">
-        <v>91599</v>
+        <v>57265</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9757,35 +9757,40 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580572</v>
+        <v>580454</v>
       </c>
       <c r="R81" t="n">
-        <v>7053336</v>
+        <v>7053253</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9812,22 +9817,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9854,7 +9859,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>114564259</v>
+        <v>114564233</v>
       </c>
       <c r="B82" t="n">
         <v>57265</v>
@@ -9891,7 +9896,7 @@
       <c r="K82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9900,10 +9905,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580489</v>
+        <v>580470</v>
       </c>
       <c r="R82" t="n">
-        <v>7053227</v>
+        <v>7053230</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9935,7 +9940,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9945,7 +9950,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9972,7 +9977,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>114564122</v>
+        <v>114564302</v>
       </c>
       <c r="B83" t="n">
         <v>57265</v>
@@ -10018,13 +10023,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580454</v>
+        <v>580503</v>
       </c>
       <c r="R83" t="n">
-        <v>7053253</v>
+        <v>7053216</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10053,7 +10058,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10063,7 +10068,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10090,10 +10095,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>114564233</v>
+        <v>114564140</v>
       </c>
       <c r="B84" t="n">
-        <v>57265</v>
+        <v>78507</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10106,40 +10111,35 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580470</v>
+        <v>580459</v>
       </c>
       <c r="R84" t="n">
-        <v>7053230</v>
+        <v>7053280</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10208,7 +10208,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>114564302</v>
+        <v>114564245</v>
       </c>
       <c r="B85" t="n">
         <v>57265</v>
@@ -10245,7 +10245,7 @@
       <c r="K85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580503</v>
+        <v>580481</v>
       </c>
       <c r="R85" t="n">
-        <v>7053216</v>
+        <v>7053209</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10326,10 +10326,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>114564140</v>
+        <v>117199380</v>
       </c>
       <c r="B86" t="n">
-        <v>78507</v>
+        <v>56496</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10338,39 +10338,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580459</v>
+        <v>580574</v>
       </c>
       <c r="R86" t="n">
-        <v>7053280</v>
+        <v>7053348</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10397,22 +10401,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10439,10 +10443,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>114564245</v>
+        <v>117202746</v>
       </c>
       <c r="B87" t="n">
-        <v>57265</v>
+        <v>90748</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10455,40 +10459,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580481</v>
+        <v>580480</v>
       </c>
       <c r="R87" t="n">
-        <v>7053209</v>
+        <v>7053304</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10515,22 +10513,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10557,10 +10555,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117199380</v>
+        <v>117199612</v>
       </c>
       <c r="B88" t="n">
-        <v>56496</v>
+        <v>56488</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10569,25 +10567,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10602,10 +10600,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580574</v>
+        <v>580498</v>
       </c>
       <c r="R88" t="n">
-        <v>7053348</v>
+        <v>7053334</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10637,7 +10635,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10647,7 +10645,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10674,10 +10672,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117202746</v>
+        <v>117200151</v>
       </c>
       <c r="B89" t="n">
-        <v>90748</v>
+        <v>90465</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10690,21 +10688,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10714,10 +10712,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>580480</v>
+        <v>580483</v>
       </c>
       <c r="R89" t="n">
-        <v>7053304</v>
+        <v>7053259</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10749,7 +10747,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10759,7 +10757,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10786,10 +10784,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117199612</v>
+        <v>117198781</v>
       </c>
       <c r="B90" t="n">
-        <v>56488</v>
+        <v>90465</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10802,39 +10800,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580498</v>
+        <v>580627</v>
       </c>
       <c r="R90" t="n">
-        <v>7053334</v>
+        <v>7053169</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10866,7 +10859,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10876,7 +10869,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10903,10 +10896,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117200151</v>
+        <v>117200334</v>
       </c>
       <c r="B91" t="n">
-        <v>90465</v>
+        <v>97802</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10915,38 +10908,42 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580483</v>
+        <v>580478</v>
       </c>
       <c r="R91" t="n">
-        <v>7053259</v>
+        <v>7053266</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10978,7 +10975,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10988,7 +10985,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11015,10 +11012,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117198781</v>
+        <v>117200140</v>
       </c>
       <c r="B92" t="n">
-        <v>90465</v>
+        <v>90907</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11027,25 +11024,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11055,10 +11052,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580627</v>
+        <v>580492</v>
       </c>
       <c r="R92" t="n">
-        <v>7053169</v>
+        <v>7053250</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11090,7 +11087,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11100,7 +11097,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11127,10 +11124,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117200334</v>
+        <v>117202760</v>
       </c>
       <c r="B93" t="n">
-        <v>97802</v>
+        <v>90465</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11139,42 +11136,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580478</v>
+        <v>580495</v>
       </c>
       <c r="R93" t="n">
-        <v>7053266</v>
+        <v>7053281</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11206,7 +11199,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11216,7 +11209,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11243,10 +11236,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117200140</v>
+        <v>118079875</v>
       </c>
       <c r="B94" t="n">
-        <v>90907</v>
+        <v>56494</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11255,38 +11248,47 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580492</v>
+        <v>580439</v>
       </c>
       <c r="R94" t="n">
-        <v>7053250</v>
+        <v>7053295</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11313,22 +11315,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11355,10 +11357,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117202760</v>
+        <v>118489062</v>
       </c>
       <c r="B95" t="n">
-        <v>90465</v>
+        <v>90531</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11371,21 +11373,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11395,10 +11397,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580495</v>
+        <v>580605</v>
       </c>
       <c r="R95" t="n">
-        <v>7053281</v>
+        <v>7053216</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11425,22 +11427,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11467,10 +11469,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118079875</v>
+        <v>118488957</v>
       </c>
       <c r="B96" t="n">
-        <v>56494</v>
+        <v>100089</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11479,47 +11481,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>102612</v>
+        <v>1365</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>580439</v>
+        <v>580589</v>
       </c>
       <c r="R96" t="n">
-        <v>7053295</v>
+        <v>7053237</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11546,22 +11539,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11588,10 +11581,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118489062</v>
+        <v>118488126</v>
       </c>
       <c r="B97" t="n">
-        <v>90531</v>
+        <v>79478</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11600,25 +11593,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11628,10 +11621,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580605</v>
+        <v>580607</v>
       </c>
       <c r="R97" t="n">
-        <v>7053216</v>
+        <v>7053151</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11663,7 +11656,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11673,7 +11666,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11700,10 +11693,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118488957</v>
+        <v>118488443</v>
       </c>
       <c r="B98" t="n">
-        <v>100089</v>
+        <v>90797</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11712,25 +11705,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1365</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11740,13 +11733,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580589</v>
+        <v>580608</v>
       </c>
       <c r="R98" t="n">
-        <v>7053237</v>
+        <v>7053200</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11773,19 +11766,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>21:01</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>21:01</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11800,22 +11783,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118488126</v>
+        <v>118488409</v>
       </c>
       <c r="B99" t="n">
-        <v>79478</v>
+        <v>90513</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11824,25 +11807,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11852,10 +11835,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580607</v>
+        <v>580602</v>
       </c>
       <c r="R99" t="n">
-        <v>7053151</v>
+        <v>7053185</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11887,7 +11870,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11897,7 +11880,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11924,10 +11907,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118488443</v>
+        <v>118488192</v>
       </c>
       <c r="B100" t="n">
-        <v>90797</v>
+        <v>57308</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11940,37 +11923,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580608</v>
+        <v>580609</v>
       </c>
       <c r="R100" t="n">
-        <v>7053200</v>
+        <v>7053171</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11997,9 +11985,19 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12014,22 +12012,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118488409</v>
+        <v>118489089</v>
       </c>
       <c r="B101" t="n">
-        <v>90513</v>
+        <v>78493</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12042,21 +12040,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12066,10 +12064,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580602</v>
+        <v>580604</v>
       </c>
       <c r="R101" t="n">
-        <v>7053185</v>
+        <v>7053205</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12101,7 +12099,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12111,7 +12109,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12138,10 +12136,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118488192</v>
+        <v>118489286</v>
       </c>
       <c r="B102" t="n">
-        <v>57308</v>
+        <v>90527</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12154,39 +12152,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580609</v>
+        <v>580600</v>
       </c>
       <c r="R102" t="n">
-        <v>7053171</v>
+        <v>7053230</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12218,7 +12211,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12228,7 +12221,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12255,10 +12248,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118489089</v>
+        <v>118488770</v>
       </c>
       <c r="B103" t="n">
-        <v>78493</v>
+        <v>97855</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12267,38 +12260,47 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580604</v>
+        <v>580601</v>
       </c>
       <c r="R103" t="n">
-        <v>7053205</v>
+        <v>7053271</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12330,7 +12332,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12340,7 +12342,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12367,10 +12369,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118489286</v>
+        <v>118488102</v>
       </c>
       <c r="B104" t="n">
-        <v>90527</v>
+        <v>90956</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12379,25 +12381,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12407,10 +12409,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580600</v>
+        <v>580607</v>
       </c>
       <c r="R104" t="n">
-        <v>7053230</v>
+        <v>7053151</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12442,7 +12444,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12452,7 +12454,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12479,10 +12481,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118488770</v>
+        <v>118488097</v>
       </c>
       <c r="B105" t="n">
-        <v>97855</v>
+        <v>90797</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12491,47 +12493,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580601</v>
+        <v>580612</v>
       </c>
       <c r="R105" t="n">
-        <v>7053271</v>
+        <v>7053150</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12563,7 +12556,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12573,7 +12566,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12600,10 +12593,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118488102</v>
+        <v>118488356</v>
       </c>
       <c r="B106" t="n">
-        <v>90956</v>
+        <v>90797</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12612,25 +12605,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12640,10 +12633,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580607</v>
+        <v>580594</v>
       </c>
       <c r="R106" t="n">
-        <v>7053151</v>
+        <v>7053187</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12675,7 +12668,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12685,7 +12678,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12712,10 +12705,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118488097</v>
+        <v>118488516</v>
       </c>
       <c r="B107" t="n">
-        <v>90797</v>
+        <v>90513</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12728,21 +12721,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12752,10 +12745,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580612</v>
+        <v>580610</v>
       </c>
       <c r="R107" t="n">
-        <v>7053150</v>
+        <v>7053237</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12787,7 +12780,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12797,7 +12790,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12824,10 +12817,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118488356</v>
+        <v>118489403</v>
       </c>
       <c r="B108" t="n">
-        <v>90797</v>
+        <v>90513</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12840,21 +12833,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12864,10 +12857,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580594</v>
+        <v>580611</v>
       </c>
       <c r="R108" t="n">
-        <v>7053187</v>
+        <v>7053232</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12899,7 +12892,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12909,7 +12902,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12936,10 +12929,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118488516</v>
+        <v>118516030</v>
       </c>
       <c r="B109" t="n">
-        <v>90513</v>
+        <v>79478</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12948,41 +12941,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Slättesmyran (Slättesmyran), Ång</t>
+          <t>Slättesmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>580610</v>
+        <v>580609</v>
       </c>
       <c r="R109" t="n">
-        <v>7053237</v>
+        <v>7053150</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13009,19 +13002,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>20:41</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>20:41</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13036,22 +13019,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118489403</v>
+        <v>118516029</v>
       </c>
       <c r="B110" t="n">
-        <v>90513</v>
+        <v>90856</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13060,41 +13043,41 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Slättesmyran (Slättesmyran), Ång</t>
+          <t>Slättesmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>580611</v>
+        <v>580614</v>
       </c>
       <c r="R110" t="n">
-        <v>7053232</v>
+        <v>7053227</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13121,19 +13104,9 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>21:17</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>21:17</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13148,22 +13121,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118516030</v>
+        <v>119116094</v>
       </c>
       <c r="B111" t="n">
-        <v>79478</v>
+        <v>90903</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13172,41 +13145,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Slättesmyrberget, Ång</t>
+          <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>580609</v>
+        <v>580598</v>
       </c>
       <c r="R111" t="n">
-        <v>7053150</v>
+        <v>7053158</v>
       </c>
       <c r="S111" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13230,12 +13203,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13250,22 +13233,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118516029</v>
+        <v>119117546</v>
       </c>
       <c r="B112" t="n">
-        <v>90856</v>
+        <v>82303</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13274,41 +13257,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Slättesmyrberget, Ång</t>
+          <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>580614</v>
+        <v>580611</v>
       </c>
       <c r="R112" t="n">
-        <v>7053227</v>
+        <v>7053222</v>
       </c>
       <c r="S112" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13332,12 +13315,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13352,22 +13345,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119116094</v>
+        <v>119116263</v>
       </c>
       <c r="B113" t="n">
-        <v>90903</v>
+        <v>78780</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13376,25 +13369,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2062</v>
+        <v>6459</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13404,10 +13397,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>580598</v>
+        <v>580586</v>
       </c>
       <c r="R113" t="n">
-        <v>7053158</v>
+        <v>7053165</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13439,7 +13432,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13449,7 +13442,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13476,10 +13469,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119117546</v>
+        <v>119116930</v>
       </c>
       <c r="B114" t="n">
-        <v>82303</v>
+        <v>90903</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13488,25 +13481,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13516,10 +13509,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>580611</v>
+        <v>580587</v>
       </c>
       <c r="R114" t="n">
-        <v>7053222</v>
+        <v>7053223</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13551,7 +13544,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13561,7 +13554,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13588,10 +13581,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119116263</v>
+        <v>119117992</v>
       </c>
       <c r="B115" t="n">
-        <v>78780</v>
+        <v>91226</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13600,41 +13593,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6459</v>
+        <v>898</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Slättesmyran (Slättesmyran), Ång</t>
+          <t>Lokal (Lokal), Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>580586</v>
+        <v>580617</v>
       </c>
       <c r="R115" t="n">
-        <v>7053165</v>
+        <v>7053220</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13661,19 +13654,9 @@
           <t>2024-08-14</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13688,22 +13671,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119116930</v>
+        <v>119116757</v>
       </c>
       <c r="B116" t="n">
-        <v>90903</v>
+        <v>95200</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13712,25 +13695,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2062</v>
+        <v>2869</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13740,10 +13723,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>580587</v>
+        <v>580605</v>
       </c>
       <c r="R116" t="n">
-        <v>7053223</v>
+        <v>7053204</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13775,7 +13758,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13785,7 +13768,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13812,10 +13795,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119117992</v>
+        <v>119116741</v>
       </c>
       <c r="B117" t="n">
-        <v>91226</v>
+        <v>74620</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13824,41 +13807,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>898</v>
+        <v>6439</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Lokal (Lokal), Ång</t>
+          <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>580617</v>
+        <v>580582</v>
       </c>
       <c r="R117" t="n">
-        <v>7053220</v>
+        <v>7053191</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13885,9 +13868,19 @@
           <t>2024-08-14</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13902,22 +13895,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119116757</v>
+        <v>119116218</v>
       </c>
       <c r="B118" t="n">
-        <v>95200</v>
+        <v>74636</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13926,25 +13919,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2869</v>
+        <v>6440</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13954,10 +13947,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>580605</v>
+        <v>580586</v>
       </c>
       <c r="R118" t="n">
-        <v>7053204</v>
+        <v>7053165</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13989,7 +13982,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13999,7 +13992,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14026,10 +14019,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119116741</v>
+        <v>119116824</v>
       </c>
       <c r="B119" t="n">
-        <v>74620</v>
+        <v>90578</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14038,25 +14031,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14066,10 +14059,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>580582</v>
+        <v>580607</v>
       </c>
       <c r="R119" t="n">
-        <v>7053191</v>
+        <v>7053184</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14101,7 +14094,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14111,7 +14104,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14138,10 +14131,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119116218</v>
+        <v>119116147</v>
       </c>
       <c r="B120" t="n">
-        <v>74636</v>
+        <v>5167</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14150,38 +14143,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Slättesmyran (Slättesmyran), Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>580586</v>
+        <v>580587</v>
       </c>
       <c r="R120" t="n">
-        <v>7053165</v>
+        <v>7053168</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14213,7 +14211,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14223,7 +14221,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14250,10 +14248,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119116824</v>
+        <v>119116252</v>
       </c>
       <c r="B121" t="n">
-        <v>90578</v>
+        <v>82303</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14266,21 +14264,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14290,10 +14288,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>580607</v>
+        <v>580586</v>
       </c>
       <c r="R121" t="n">
-        <v>7053184</v>
+        <v>7053165</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14325,7 +14323,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14335,7 +14333,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14362,10 +14360,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119116147</v>
+        <v>119175371</v>
       </c>
       <c r="B122" t="n">
-        <v>5167</v>
+        <v>57461</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14374,31 +14372,31 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14407,13 +14405,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>580587</v>
+        <v>580634</v>
       </c>
       <c r="R122" t="n">
-        <v>7053168</v>
+        <v>7053199</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14437,22 +14435,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14467,22 +14455,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119116252</v>
+        <v>119117730</v>
       </c>
       <c r="B123" t="n">
-        <v>82303</v>
+        <v>91290</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14491,41 +14479,41 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1312</v>
+        <v>1105</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Slättesmyran (Slättesmyran), Ång</t>
+          <t>Lokal, Lokal, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>580586</v>
+        <v>580588</v>
       </c>
       <c r="R123" t="n">
-        <v>7053165</v>
+        <v>7053208</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14552,19 +14540,9 @@
           <t>2024-08-14</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14579,22 +14557,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119175371</v>
+        <v>120896228</v>
       </c>
       <c r="B124" t="n">
-        <v>57461</v>
+        <v>90711</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14607,42 +14585,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Slättesmyran (Slättesmyran), Ång</t>
+          <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>580634</v>
+        <v>580486</v>
       </c>
       <c r="R124" t="n">
-        <v>7053199</v>
+        <v>7053298</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14666,12 +14639,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14686,22 +14669,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119117730</v>
+        <v>120896380</v>
       </c>
       <c r="B125" t="n">
-        <v>91290</v>
+        <v>91137</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14714,37 +14697,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1105</v>
+        <v>1209</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lokal, Lokal, Ång</t>
+          <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>580588</v>
+        <v>580477</v>
       </c>
       <c r="R125" t="n">
-        <v>7053208</v>
+        <v>7053274</v>
       </c>
       <c r="S125" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14768,12 +14751,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14788,22 +14771,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120896228</v>
+        <v>120896391</v>
       </c>
       <c r="B126" t="n">
-        <v>90711</v>
+        <v>82385</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14816,21 +14799,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14840,10 +14823,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>580486</v>
+        <v>580499</v>
       </c>
       <c r="R126" t="n">
-        <v>7053298</v>
+        <v>7053308</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14875,7 +14858,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14885,7 +14868,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14912,10 +14895,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120896380</v>
+        <v>120895803</v>
       </c>
       <c r="B127" t="n">
-        <v>91137</v>
+        <v>100320</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14924,25 +14907,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1209</v>
+        <v>1365</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14952,10 +14935,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>580477</v>
+        <v>580463</v>
       </c>
       <c r="R127" t="n">
-        <v>7053274</v>
+        <v>7053312</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14985,9 +14968,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15002,22 +14995,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120896391</v>
+        <v>120896442</v>
       </c>
       <c r="B128" t="n">
-        <v>82385</v>
+        <v>90662</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15026,25 +15019,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15054,10 +15047,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>580499</v>
+        <v>580500</v>
       </c>
       <c r="R128" t="n">
-        <v>7053308</v>
+        <v>7053305</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15089,7 +15082,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15099,7 +15092,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15126,10 +15119,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120895803</v>
+        <v>120895507</v>
       </c>
       <c r="B129" t="n">
-        <v>100320</v>
+        <v>78601</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15138,25 +15131,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15166,13 +15159,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>580463</v>
+        <v>580500</v>
       </c>
       <c r="R129" t="n">
-        <v>7053312</v>
+        <v>7053335</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15199,19 +15192,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15226,22 +15209,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120896442</v>
+        <v>120895561</v>
       </c>
       <c r="B130" t="n">
-        <v>90662</v>
+        <v>95375</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15254,21 +15237,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15278,10 +15261,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>580500</v>
+        <v>580472</v>
       </c>
       <c r="R130" t="n">
-        <v>7053305</v>
+        <v>7053314</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15313,7 +15296,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15323,7 +15306,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15350,10 +15333,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120895507</v>
+        <v>120896185</v>
       </c>
       <c r="B131" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15366,21 +15349,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15390,13 +15373,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>580500</v>
+        <v>580483</v>
       </c>
       <c r="R131" t="n">
-        <v>7053335</v>
+        <v>7053297</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15423,9 +15406,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15440,19 +15433,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120895561</v>
+        <v>120896112</v>
       </c>
       <c r="B132" t="n">
         <v>95375</v>
@@ -15488,17 +15481,17 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Slättesmyran, Slättesmyran, Ång</t>
+          <t>Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>580472</v>
+        <v>580482</v>
       </c>
       <c r="R132" t="n">
-        <v>7053314</v>
+        <v>7053297</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15527,7 +15520,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15537,7 +15530,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15564,10 +15557,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120896185</v>
+        <v>120897756</v>
       </c>
       <c r="B133" t="n">
-        <v>90697</v>
+        <v>90644</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15580,21 +15573,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15604,10 +15597,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>580483</v>
+        <v>580487</v>
       </c>
       <c r="R133" t="n">
-        <v>7053297</v>
+        <v>7053274</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15639,7 +15632,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15649,7 +15642,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15676,53 +15669,53 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120896112</v>
+        <v>120896287</v>
       </c>
       <c r="B134" t="n">
-        <v>95375</v>
+        <v>91194</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2869</v>
+        <v>1209</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Slättesmyran, Ång</t>
+          <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>580482</v>
+        <v>580488</v>
       </c>
       <c r="R134" t="n">
-        <v>7053297</v>
+        <v>7053300</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15751,7 +15744,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15761,7 +15754,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15788,7 +15781,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120897756</v>
+        <v>120897746</v>
       </c>
       <c r="B135" t="n">
         <v>90644</v>
@@ -15828,13 +15821,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>580487</v>
+        <v>580486</v>
       </c>
       <c r="R135" t="n">
-        <v>7053274</v>
+        <v>7053291</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15861,19 +15854,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15888,49 +15871,44 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120896287</v>
+        <v>120896940</v>
       </c>
       <c r="B136" t="n">
-        <v>91194</v>
+        <v>91089</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15940,10 +15918,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>580488</v>
+        <v>580477</v>
       </c>
       <c r="R136" t="n">
-        <v>7053300</v>
+        <v>7053259</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15975,7 +15953,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15985,7 +15963,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16012,10 +15995,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120897746</v>
+        <v>120895782</v>
       </c>
       <c r="B137" t="n">
-        <v>90644</v>
+        <v>95375</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16024,25 +16007,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>112</v>
+        <v>2869</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16052,13 +16035,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>580486</v>
+        <v>580458</v>
       </c>
       <c r="R137" t="n">
-        <v>7053291</v>
+        <v>7053304</v>
       </c>
       <c r="S137" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16114,10 +16097,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120896940</v>
+        <v>120897610</v>
       </c>
       <c r="B138" t="n">
-        <v>91089</v>
+        <v>98081</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16126,20 +16109,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6040162</v>
+        <v>220787</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16149,13 +16137,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>580477</v>
+        <v>580489</v>
       </c>
       <c r="R138" t="n">
-        <v>7053259</v>
+        <v>7053263</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16182,24 +16170,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>På tallåga</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16214,22 +16187,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120895782</v>
+        <v>120895896</v>
       </c>
       <c r="B139" t="n">
-        <v>95375</v>
+        <v>90662</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16242,21 +16215,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16272,7 +16245,7 @@
         <v>7053304</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16328,10 +16301,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120897610</v>
+        <v>120897551</v>
       </c>
       <c r="B140" t="n">
-        <v>98081</v>
+        <v>95375</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16340,25 +16313,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16368,10 +16341,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>580489</v>
+        <v>580492</v>
       </c>
       <c r="R140" t="n">
-        <v>7053263</v>
+        <v>7053272</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16430,10 +16403,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120895896</v>
+        <v>120897183</v>
       </c>
       <c r="B141" t="n">
-        <v>90662</v>
+        <v>91973</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16446,21 +16419,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16470,13 +16443,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>580458</v>
+        <v>580490</v>
       </c>
       <c r="R141" t="n">
-        <v>7053304</v>
+        <v>7053233</v>
       </c>
       <c r="S141" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16532,10 +16505,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120897551</v>
+        <v>121126181</v>
       </c>
       <c r="B142" t="n">
-        <v>95375</v>
+        <v>95392</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16572,13 +16545,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>580492</v>
+        <v>580568</v>
       </c>
       <c r="R142" t="n">
-        <v>7053272</v>
+        <v>7053195</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16602,12 +16575,22 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16622,22 +16605,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120897183</v>
+        <v>121126214</v>
       </c>
       <c r="B143" t="n">
-        <v>91973</v>
+        <v>78607</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16646,25 +16629,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16674,10 +16657,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>580490</v>
+        <v>580564</v>
       </c>
       <c r="R143" t="n">
-        <v>7053233</v>
+        <v>7053209</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16704,12 +16687,22 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16724,22 +16717,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121126181</v>
+        <v>121127030</v>
       </c>
       <c r="B144" t="n">
-        <v>95392</v>
+        <v>78607</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16748,25 +16741,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16776,10 +16769,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>580568</v>
+        <v>580528</v>
       </c>
       <c r="R144" t="n">
-        <v>7053195</v>
+        <v>7053255</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16811,7 +16804,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16821,7 +16814,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16848,10 +16841,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121126214</v>
+        <v>121127278</v>
       </c>
       <c r="B145" t="n">
-        <v>78607</v>
+        <v>90678</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16860,25 +16853,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16888,10 +16881,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>580564</v>
+        <v>580510</v>
       </c>
       <c r="R145" t="n">
-        <v>7053209</v>
+        <v>7053247</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16923,7 +16916,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16933,7 +16926,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16960,10 +16953,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121127030</v>
+        <v>121126868</v>
       </c>
       <c r="B146" t="n">
-        <v>78607</v>
+        <v>91105</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16976,21 +16969,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -17000,10 +16988,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>580528</v>
+        <v>580542</v>
       </c>
       <c r="R146" t="n">
-        <v>7053255</v>
+        <v>7053234</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17035,7 +17023,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17045,7 +17033,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17060,22 +17048,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121127278</v>
+        <v>121127610</v>
       </c>
       <c r="B147" t="n">
-        <v>90678</v>
+        <v>91989</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17088,21 +17076,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17112,10 +17100,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>580510</v>
+        <v>580433</v>
       </c>
       <c r="R147" t="n">
-        <v>7053247</v>
+        <v>7053267</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17147,7 +17135,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17157,7 +17145,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17184,10 +17172,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121126868</v>
+        <v>121126027</v>
       </c>
       <c r="B148" t="n">
-        <v>91105</v>
+        <v>57354</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17200,29 +17188,44 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6040162</v>
+        <v>100109</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>580542</v>
+        <v>580590</v>
       </c>
       <c r="R148" t="n">
-        <v>7053234</v>
+        <v>7053152</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17254,7 +17257,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17264,7 +17267,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17279,22 +17282,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121127610</v>
+        <v>121127803</v>
       </c>
       <c r="B149" t="n">
-        <v>91989</v>
+        <v>56566</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17307,34 +17310,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>580433</v>
+        <v>580418</v>
       </c>
       <c r="R149" t="n">
-        <v>7053267</v>
+        <v>7053258</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17366,7 +17374,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17376,7 +17384,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17403,10 +17411,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121126027</v>
+        <v>121129042</v>
       </c>
       <c r="B150" t="n">
-        <v>57354</v>
+        <v>91981</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17419,44 +17427,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>580590</v>
+        <v>580421</v>
       </c>
       <c r="R150" t="n">
-        <v>7053152</v>
+        <v>7053299</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17488,7 +17486,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17498,7 +17496,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17525,10 +17523,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121127803</v>
+        <v>121126610</v>
       </c>
       <c r="B151" t="n">
-        <v>56566</v>
+        <v>98098</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17537,31 +17535,30 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17570,10 +17567,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>580418</v>
+        <v>580564</v>
       </c>
       <c r="R151" t="n">
-        <v>7053258</v>
+        <v>7053248</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17605,7 +17602,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17615,7 +17612,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17630,19 +17627,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121129042</v>
+        <v>121127710</v>
       </c>
       <c r="B152" t="n">
         <v>91981</v>
@@ -17682,10 +17679,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>580421</v>
+        <v>580426</v>
       </c>
       <c r="R152" t="n">
-        <v>7053299</v>
+        <v>7053263</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17717,7 +17714,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17727,7 +17724,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17754,10 +17751,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121126610</v>
+        <v>121126643</v>
       </c>
       <c r="B153" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17766,42 +17763,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>580564</v>
+        <v>580565</v>
       </c>
       <c r="R153" t="n">
-        <v>7053248</v>
+        <v>7053263</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17833,7 +17826,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17843,7 +17836,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17858,22 +17851,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121127710</v>
+        <v>121127564</v>
       </c>
       <c r="B154" t="n">
-        <v>91981</v>
+        <v>91989</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17882,25 +17875,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17910,10 +17903,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>580426</v>
+        <v>580441</v>
       </c>
       <c r="R154" t="n">
-        <v>7053263</v>
+        <v>7053267</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17945,7 +17938,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17955,7 +17948,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17982,10 +17975,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121126643</v>
+        <v>121125921</v>
       </c>
       <c r="B155" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17998,34 +17991,44 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>580565</v>
+        <v>580600</v>
       </c>
       <c r="R155" t="n">
-        <v>7053263</v>
+        <v>7053106</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18057,7 +18060,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18067,7 +18070,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18094,10 +18097,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121127564</v>
+        <v>121126876</v>
       </c>
       <c r="B156" t="n">
-        <v>91989</v>
+        <v>78607</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18106,25 +18109,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18134,10 +18137,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>580441</v>
+        <v>580540</v>
       </c>
       <c r="R156" t="n">
-        <v>7053267</v>
+        <v>7053257</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18169,7 +18172,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18179,7 +18182,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18206,10 +18209,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121125921</v>
+        <v>121127289</v>
       </c>
       <c r="B157" t="n">
-        <v>57354</v>
+        <v>95392</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18218,48 +18221,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>580600</v>
+        <v>580508</v>
       </c>
       <c r="R157" t="n">
-        <v>7053106</v>
+        <v>7053256</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18291,7 +18284,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18301,7 +18294,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18328,10 +18321,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121126876</v>
+        <v>121126972</v>
       </c>
       <c r="B158" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18344,21 +18337,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18368,10 +18361,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>580540</v>
+        <v>580535</v>
       </c>
       <c r="R158" t="n">
-        <v>7053257</v>
+        <v>7053234</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18403,7 +18396,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18413,7 +18406,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18440,10 +18433,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121127289</v>
+        <v>121129017</v>
       </c>
       <c r="B159" t="n">
-        <v>95392</v>
+        <v>91989</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18456,21 +18449,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18480,10 +18473,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>580508</v>
+        <v>580426</v>
       </c>
       <c r="R159" t="n">
-        <v>7053256</v>
+        <v>7053283</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18515,7 +18508,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18525,7 +18518,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18552,10 +18545,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121126972</v>
+        <v>121125943</v>
       </c>
       <c r="B160" t="n">
-        <v>82391</v>
+        <v>98098</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18564,25 +18557,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18592,10 +18585,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>580535</v>
+        <v>580603</v>
       </c>
       <c r="R160" t="n">
-        <v>7053234</v>
+        <v>7053117</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18627,7 +18620,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18637,7 +18630,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18664,10 +18657,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121129017</v>
+        <v>121126530</v>
       </c>
       <c r="B161" t="n">
-        <v>91989</v>
+        <v>78607</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18676,25 +18669,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18704,10 +18697,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>580426</v>
+        <v>580571</v>
       </c>
       <c r="R161" t="n">
-        <v>7053283</v>
+        <v>7053237</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18739,7 +18732,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18749,7 +18742,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18776,10 +18769,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121125943</v>
+        <v>121126779</v>
       </c>
       <c r="B162" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18788,25 +18781,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18816,10 +18809,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>580603</v>
+        <v>580548</v>
       </c>
       <c r="R162" t="n">
-        <v>7053117</v>
+        <v>7053237</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18851,7 +18844,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18861,7 +18854,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18888,10 +18881,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121126530</v>
+        <v>121128867</v>
       </c>
       <c r="B163" t="n">
-        <v>78607</v>
+        <v>95392</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18900,25 +18893,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18928,10 +18921,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>580571</v>
+        <v>580445</v>
       </c>
       <c r="R163" t="n">
-        <v>7053237</v>
+        <v>7053311</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18963,7 +18956,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18973,7 +18966,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19000,10 +18993,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121126779</v>
+        <v>121128951</v>
       </c>
       <c r="B164" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19016,21 +19009,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19040,10 +19033,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>580548</v>
+        <v>580424</v>
       </c>
       <c r="R164" t="n">
-        <v>7053237</v>
+        <v>7053312</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19075,7 +19068,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19085,7 +19078,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19112,10 +19105,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121128867</v>
+        <v>121126694</v>
       </c>
       <c r="B165" t="n">
-        <v>95392</v>
+        <v>98098</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19124,38 +19117,42 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Slättesmyran, Slättesmyran, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>580445</v>
+        <v>580565</v>
       </c>
       <c r="R165" t="n">
-        <v>7053311</v>
+        <v>7053263</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19187,7 +19184,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19197,7 +19194,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19221,234 +19218,6 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>121128951</v>
-      </c>
-      <c r="B166" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>Slättesmyran, Slättesmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q166" t="n">
-        <v>580424</v>
-      </c>
-      <c r="R166" t="n">
-        <v>7053312</v>
-      </c>
-      <c r="S166" t="n">
-        <v>10</v>
-      </c>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AD166" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE166" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG166" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT166" t="inlineStr"/>
-      <c r="AW166" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX166" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>121126694</v>
-      </c>
-      <c r="B167" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E167" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>Slättesmyran, Slättesmyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q167" t="n">
-        <v>580565</v>
-      </c>
-      <c r="R167" t="n">
-        <v>7053263</v>
-      </c>
-      <c r="S167" t="n">
-        <v>10</v>
-      </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>Ramsele</t>
-        </is>
-      </c>
-      <c r="Y167" t="inlineStr">
-        <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AD167" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE167" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG167" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT167" t="inlineStr"/>
-      <c r="AW167" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX167" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY167" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
